--- a/data/nzd0008/nzd0008.xlsx
+++ b/data/nzd0008/nzd0008.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ225"/>
+  <dimension ref="A1:AJ226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26052,6 +26052,120 @@
         <v>314.43</v>
       </c>
       <c r="AJ225" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>366.18</v>
+      </c>
+      <c r="C226" t="n">
+        <v>335.74</v>
+      </c>
+      <c r="D226" t="n">
+        <v>337.04</v>
+      </c>
+      <c r="E226" t="n">
+        <v>349.69</v>
+      </c>
+      <c r="F226" t="n">
+        <v>358.17</v>
+      </c>
+      <c r="G226" t="n">
+        <v>374.91</v>
+      </c>
+      <c r="H226" t="n">
+        <v>370.32</v>
+      </c>
+      <c r="I226" t="n">
+        <v>368.3</v>
+      </c>
+      <c r="J226" t="n">
+        <v>374.49</v>
+      </c>
+      <c r="K226" t="n">
+        <v>376.7</v>
+      </c>
+      <c r="L226" t="n">
+        <v>375.73</v>
+      </c>
+      <c r="M226" t="n">
+        <v>370.83</v>
+      </c>
+      <c r="N226" t="n">
+        <v>374</v>
+      </c>
+      <c r="O226" t="n">
+        <v>376.43</v>
+      </c>
+      <c r="P226" t="n">
+        <v>383.68</v>
+      </c>
+      <c r="Q226" t="n">
+        <v>389.91</v>
+      </c>
+      <c r="R226" t="n">
+        <v>392.16</v>
+      </c>
+      <c r="S226" t="n">
+        <v>391.84</v>
+      </c>
+      <c r="T226" t="n">
+        <v>390.58</v>
+      </c>
+      <c r="U226" t="n">
+        <v>390.82</v>
+      </c>
+      <c r="V226" t="n">
+        <v>391.39</v>
+      </c>
+      <c r="W226" t="n">
+        <v>394.18</v>
+      </c>
+      <c r="X226" t="n">
+        <v>398.95</v>
+      </c>
+      <c r="Y226" t="n">
+        <v>396.25</v>
+      </c>
+      <c r="Z226" t="n">
+        <v>387.76</v>
+      </c>
+      <c r="AA226" t="n">
+        <v>380.4</v>
+      </c>
+      <c r="AB226" t="n">
+        <v>380.23</v>
+      </c>
+      <c r="AC226" t="n">
+        <v>375.8</v>
+      </c>
+      <c r="AD226" t="n">
+        <v>375.05</v>
+      </c>
+      <c r="AE226" t="n">
+        <v>375.03</v>
+      </c>
+      <c r="AF226" t="n">
+        <v>349.52</v>
+      </c>
+      <c r="AG226" t="n">
+        <v>339.07</v>
+      </c>
+      <c r="AH226" t="n">
+        <v>333.68</v>
+      </c>
+      <c r="AI226" t="n">
+        <v>309.88</v>
+      </c>
+      <c r="AJ226" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -26068,7 +26182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B226"/>
+  <dimension ref="A1:B227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28331,6 +28445,16 @@
       </c>
       <c r="B226" t="n">
         <v>0.28</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>
@@ -28499,28 +28623,28 @@
         <v>0.0307</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2366826189797137</v>
+        <v>-0.2394711759192466</v>
       </c>
       <c r="J2" t="n">
+        <v>225</v>
+      </c>
+      <c r="K2" t="n">
         <v>224</v>
       </c>
-      <c r="K2" t="n">
-        <v>223</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.02745923049539101</v>
+        <v>0.02835934058278999</v>
       </c>
       <c r="M2" t="n">
-        <v>8.241976457251218</v>
+        <v>8.222176251851536</v>
       </c>
       <c r="N2" t="n">
-        <v>130.2794754723006</v>
+        <v>129.7482439220466</v>
       </c>
       <c r="O2" t="n">
-        <v>11.41400348135134</v>
+        <v>11.39070866636693</v>
       </c>
       <c r="P2" t="n">
-        <v>375.7908590540383</v>
+        <v>375.8151133880185</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28577,28 +28701,28 @@
         <v>0.0407</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3590843990489159</v>
+        <v>-0.3684938734765952</v>
       </c>
       <c r="J3" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K3" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1096051849919664</v>
+        <v>0.1149412288969532</v>
       </c>
       <c r="M3" t="n">
-        <v>6.328525294066585</v>
+        <v>6.349058146943312</v>
       </c>
       <c r="N3" t="n">
-        <v>68.91234785002109</v>
+        <v>69.18032935226499</v>
       </c>
       <c r="O3" t="n">
-        <v>8.301346146862031</v>
+        <v>8.317471331616659</v>
       </c>
       <c r="P3" t="n">
-        <v>356.6327611396864</v>
+        <v>356.7142771645394</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28655,28 +28779,28 @@
         <v>0.0421</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3073121815063303</v>
+        <v>-0.3110983642388629</v>
       </c>
       <c r="J4" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K4" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09808550891913426</v>
+        <v>0.1010443731319896</v>
       </c>
       <c r="M4" t="n">
-        <v>6.095714659063676</v>
+        <v>6.089185932666729</v>
       </c>
       <c r="N4" t="n">
-        <v>57.13109076889319</v>
+        <v>56.97015274976256</v>
       </c>
       <c r="O4" t="n">
-        <v>7.558511147633057</v>
+        <v>7.547857494002027</v>
       </c>
       <c r="P4" t="n">
-        <v>349.7287926692736</v>
+        <v>349.7615930735997</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28733,28 +28857,28 @@
         <v>0.0379</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2473060959857731</v>
+        <v>-0.2445653193781027</v>
       </c>
       <c r="J5" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K5" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07231869615714037</v>
+        <v>0.0714456021551545</v>
       </c>
       <c r="M5" t="n">
-        <v>5.777708458027831</v>
+        <v>5.765292029108084</v>
       </c>
       <c r="N5" t="n">
-        <v>51.61433182671011</v>
+        <v>51.43365667841572</v>
       </c>
       <c r="O5" t="n">
-        <v>7.184311506797997</v>
+        <v>7.171726199348084</v>
       </c>
       <c r="P5" t="n">
-        <v>352.856900542885</v>
+        <v>352.8331566860114</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28811,28 +28935,28 @@
         <v>0.0309</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3205733972849512</v>
+        <v>-0.3153991979211125</v>
       </c>
       <c r="J6" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K6" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09043136076247682</v>
+        <v>0.08839948088104876</v>
       </c>
       <c r="M6" t="n">
-        <v>6.530920990331587</v>
+        <v>6.528050036979137</v>
       </c>
       <c r="N6" t="n">
-        <v>68.00233435060431</v>
+        <v>67.87374707814666</v>
       </c>
       <c r="O6" t="n">
-        <v>8.246352790816333</v>
+        <v>8.23855248682356</v>
       </c>
       <c r="P6" t="n">
-        <v>360.3063456062463</v>
+        <v>360.2615205560079</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28889,28 +29013,28 @@
         <v>0.0305</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1886248411401232</v>
+        <v>-0.1809706969265717</v>
       </c>
       <c r="J7" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K7" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01958760794773107</v>
+        <v>0.01818101333771716</v>
       </c>
       <c r="M7" t="n">
-        <v>8.663192736009302</v>
+        <v>8.665035357220065</v>
       </c>
       <c r="N7" t="n">
-        <v>117.1595278567206</v>
+        <v>117.0188069993177</v>
       </c>
       <c r="O7" t="n">
-        <v>10.82402549224273</v>
+        <v>10.81752314531001</v>
       </c>
       <c r="P7" t="n">
-        <v>370.5542531843237</v>
+        <v>370.4879439111825</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28967,28 +29091,28 @@
         <v>0.0362</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2092695493875435</v>
+        <v>-0.2021343633129424</v>
       </c>
       <c r="J8" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K8" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03507412863464354</v>
+        <v>0.03299030327791741</v>
       </c>
       <c r="M8" t="n">
-        <v>7.219175042788889</v>
+        <v>7.233007495656977</v>
       </c>
       <c r="N8" t="n">
-        <v>79.26319759008547</v>
+        <v>79.24112455526445</v>
       </c>
       <c r="O8" t="n">
-        <v>8.902988127032714</v>
+        <v>8.901748398784614</v>
       </c>
       <c r="P8" t="n">
-        <v>367.1399431766737</v>
+        <v>367.0781297342909</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29045,28 +29169,28 @@
         <v>0.0308</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4671577023866934</v>
+        <v>-0.4562992801607044</v>
       </c>
       <c r="J9" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K9" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09609231263927853</v>
+        <v>0.09245879240163757</v>
       </c>
       <c r="M9" t="n">
-        <v>9.294857081103986</v>
+        <v>9.315230429805231</v>
       </c>
       <c r="N9" t="n">
-        <v>135.0563199025877</v>
+        <v>135.2208032905745</v>
       </c>
       <c r="O9" t="n">
-        <v>11.62137340862033</v>
+        <v>11.62844801727963</v>
       </c>
       <c r="P9" t="n">
-        <v>367.376330426765</v>
+        <v>367.2822618979814</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29123,28 +29247,28 @@
         <v>0.0363</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5944920265823158</v>
+        <v>-0.5829977812198223</v>
       </c>
       <c r="J10" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K10" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1701021121263389</v>
+        <v>0.1650172250318577</v>
       </c>
       <c r="M10" t="n">
-        <v>8.867311731674562</v>
+        <v>8.89327919263175</v>
       </c>
       <c r="N10" t="n">
-        <v>113.4382377516166</v>
+        <v>113.7909827275296</v>
       </c>
       <c r="O10" t="n">
-        <v>10.65073883595015</v>
+        <v>10.6672856307277</v>
       </c>
       <c r="P10" t="n">
-        <v>376.136612761777</v>
+        <v>376.0370359790526</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29201,28 +29325,28 @@
         <v>0.0417</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6821928944097218</v>
+        <v>-0.6708948087955292</v>
       </c>
       <c r="J11" t="n">
+        <v>225</v>
+      </c>
+      <c r="K11" t="n">
         <v>224</v>
       </c>
-      <c r="K11" t="n">
-        <v>223</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.2032872611522059</v>
+        <v>0.1984451343462083</v>
       </c>
       <c r="M11" t="n">
-        <v>8.86144695213734</v>
+        <v>8.883552898185476</v>
       </c>
       <c r="N11" t="n">
-        <v>120.5266868046408</v>
+        <v>120.820653572112</v>
       </c>
       <c r="O11" t="n">
-        <v>10.97846468339908</v>
+        <v>10.99184486663235</v>
       </c>
       <c r="P11" t="n">
-        <v>380.8887435786975</v>
+        <v>380.791112401272</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -29279,28 +29403,28 @@
         <v>0.035</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7399667760461227</v>
+        <v>-0.73014179504886</v>
       </c>
       <c r="J12" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K12" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1990214973082171</v>
+        <v>0.195699983886046</v>
       </c>
       <c r="M12" t="n">
-        <v>9.556214742576607</v>
+        <v>9.565373174688835</v>
       </c>
       <c r="N12" t="n">
-        <v>145.5605650554182</v>
+        <v>145.5388589378433</v>
       </c>
       <c r="O12" t="n">
-        <v>12.06484832293462</v>
+        <v>12.06394872907885</v>
       </c>
       <c r="P12" t="n">
-        <v>383.2488692464281</v>
+        <v>383.1636676025623</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -29357,28 +29481,28 @@
         <v>0.0377</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.9488618469620147</v>
+        <v>-0.9438538518569726</v>
       </c>
       <c r="J13" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K13" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2746291173709908</v>
+        <v>0.2743216583407561</v>
       </c>
       <c r="M13" t="n">
-        <v>10.24081288130527</v>
+        <v>10.22159737858781</v>
       </c>
       <c r="N13" t="n">
-        <v>157.5092491154927</v>
+        <v>156.9644732890229</v>
       </c>
       <c r="O13" t="n">
-        <v>12.55026888618299</v>
+        <v>12.52854633582935</v>
       </c>
       <c r="P13" t="n">
-        <v>389.6985154009901</v>
+        <v>389.6550961915793</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -29435,28 +29559,28 @@
         <v>0.0472</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8957153392569036</v>
+        <v>-0.89254183713792</v>
       </c>
       <c r="J14" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K14" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3221821105708778</v>
+        <v>0.3227058128922525</v>
       </c>
       <c r="M14" t="n">
-        <v>8.482044564498469</v>
+        <v>8.460006966818057</v>
       </c>
       <c r="N14" t="n">
-        <v>111.7990679954263</v>
+        <v>111.3616155805094</v>
       </c>
       <c r="O14" t="n">
-        <v>10.57350783777202</v>
+        <v>10.55280131436717</v>
       </c>
       <c r="P14" t="n">
-        <v>393.7030070715908</v>
+        <v>393.6754928767524</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -29513,28 +29637,28 @@
         <v>0.0445</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.043221092024559</v>
+        <v>-1.039153984687942</v>
       </c>
       <c r="J15" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K15" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3778510883232213</v>
+        <v>0.3781809471982265</v>
       </c>
       <c r="M15" t="n">
-        <v>8.718144443906528</v>
+        <v>8.701800331619735</v>
       </c>
       <c r="N15" t="n">
-        <v>117.8443259461496</v>
+        <v>117.4136530014635</v>
       </c>
       <c r="O15" t="n">
-        <v>10.85561264720465</v>
+        <v>10.83575807230225</v>
       </c>
       <c r="P15" t="n">
-        <v>398.9881758672936</v>
+        <v>398.952527965597</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -29591,28 +29715,28 @@
         <v>0.0452</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9522285738783696</v>
+        <v>-0.9465833356186497</v>
       </c>
       <c r="J16" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K16" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3441557521816526</v>
+        <v>0.3433460121722939</v>
       </c>
       <c r="M16" t="n">
-        <v>8.645704909829238</v>
+        <v>8.639994550536398</v>
       </c>
       <c r="N16" t="n">
-        <v>113.6345483102382</v>
+        <v>113.32264262972</v>
       </c>
       <c r="O16" t="n">
-        <v>10.65995067109779</v>
+        <v>10.64531082823419</v>
       </c>
       <c r="P16" t="n">
-        <v>401.9452790991523</v>
+        <v>401.8957989940356</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -29669,28 +29793,28 @@
         <v>0.0472</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9466649254321166</v>
+        <v>-0.9383223462115223</v>
       </c>
       <c r="J17" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K17" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3644760764843519</v>
+        <v>0.3616944600045779</v>
       </c>
       <c r="M17" t="n">
-        <v>8.141863280448177</v>
+        <v>8.154867257306432</v>
       </c>
       <c r="N17" t="n">
-        <v>103.0940494275086</v>
+        <v>103.0825077561277</v>
       </c>
       <c r="O17" t="n">
-        <v>10.15352399059108</v>
+        <v>10.15295561677129</v>
       </c>
       <c r="P17" t="n">
-        <v>404.713735067316</v>
+        <v>404.6410120034035</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -29747,28 +29871,28 @@
         <v>0.0468</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.043607297215727</v>
+        <v>-1.033591590868032</v>
       </c>
       <c r="J18" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K18" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3917615212805895</v>
+        <v>0.3881750131359483</v>
       </c>
       <c r="M18" t="n">
-        <v>8.516714832466709</v>
+        <v>8.538209126435287</v>
       </c>
       <c r="N18" t="n">
-        <v>111.5589652378063</v>
+        <v>111.709901227416</v>
       </c>
       <c r="O18" t="n">
-        <v>10.56214775686301</v>
+        <v>10.56929047890236</v>
       </c>
       <c r="P18" t="n">
-        <v>407.4903166934189</v>
+        <v>407.4030088197276</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -29825,28 +29949,28 @@
         <v>0.0452</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.089063344073726</v>
+        <v>-1.079138721742054</v>
       </c>
       <c r="J19" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K19" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4184636313272867</v>
+        <v>0.4150408482412825</v>
       </c>
       <c r="M19" t="n">
-        <v>8.568168764757814</v>
+        <v>8.582900235158407</v>
       </c>
       <c r="N19" t="n">
-        <v>107.9996226237806</v>
+        <v>108.1524107256425</v>
       </c>
       <c r="O19" t="n">
-        <v>10.39228668887558</v>
+        <v>10.39963512463983</v>
       </c>
       <c r="P19" t="n">
-        <v>408.4778901435412</v>
+        <v>408.3912078863675</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -29903,28 +30027,28 @@
         <v>0.0417</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.002545133037144</v>
+        <v>-0.9941769433671618</v>
       </c>
       <c r="J20" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K20" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3162199320303577</v>
+        <v>0.3141047303955414</v>
       </c>
       <c r="M20" t="n">
-        <v>9.822330562148275</v>
+        <v>9.820149378463856</v>
       </c>
       <c r="N20" t="n">
-        <v>142.9840228729701</v>
+        <v>142.8027306699341</v>
       </c>
       <c r="O20" t="n">
-        <v>11.95759268719963</v>
+        <v>11.95000965145778</v>
       </c>
       <c r="P20" t="n">
-        <v>406.7679549544812</v>
+        <v>406.6954597729112</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -29981,28 +30105,28 @@
         <v>0.0364</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.37617452037303</v>
+        <v>-1.366604897081647</v>
       </c>
       <c r="J21" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K21" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4964324775512036</v>
+        <v>0.4943036005474023</v>
       </c>
       <c r="M21" t="n">
-        <v>9.183473246942176</v>
+        <v>9.202094973952974</v>
       </c>
       <c r="N21" t="n">
-        <v>126.3854274394063</v>
+        <v>126.4176870981549</v>
       </c>
       <c r="O21" t="n">
-        <v>11.24212735381548</v>
+        <v>11.24356202891926</v>
       </c>
       <c r="P21" t="n">
-        <v>415.3765883344703</v>
+        <v>415.2936849102621</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -30059,28 +30183,28 @@
         <v>0.041</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.423791197543754</v>
+        <v>-1.415629265498546</v>
       </c>
       <c r="J22" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K22" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5804867731232963</v>
+        <v>0.5790635872458905</v>
       </c>
       <c r="M22" t="n">
-        <v>8.089158383369517</v>
+        <v>8.10653115492085</v>
       </c>
       <c r="N22" t="n">
-        <v>96.38254436215</v>
+        <v>96.38625606866516</v>
       </c>
       <c r="O22" t="n">
-        <v>9.817461197384485</v>
+        <v>9.817650231530209</v>
       </c>
       <c r="P22" t="n">
-        <v>418.9110502363515</v>
+        <v>418.840341902899</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -30137,28 +30261,28 @@
         <v>0.0413</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.185064126115984</v>
+        <v>-1.178540889180409</v>
       </c>
       <c r="J23" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K23" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5243528599512125</v>
+        <v>0.5233071460921315</v>
       </c>
       <c r="M23" t="n">
-        <v>7.515113775118031</v>
+        <v>7.521332530885607</v>
       </c>
       <c r="N23" t="n">
-        <v>83.81030119900184</v>
+        <v>83.71380715989123</v>
       </c>
       <c r="O23" t="n">
-        <v>9.154796622481673</v>
+        <v>9.149524969083981</v>
       </c>
       <c r="P23" t="n">
-        <v>417.4142683853583</v>
+        <v>417.3577563720414</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -30215,28 +30339,28 @@
         <v>0.0373</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.203110216265905</v>
+        <v>-1.193864673311333</v>
       </c>
       <c r="J24" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K24" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4825082105945016</v>
+        <v>0.4798327133624916</v>
       </c>
       <c r="M24" t="n">
-        <v>8.231674574323364</v>
+        <v>8.242415598067087</v>
       </c>
       <c r="N24" t="n">
-        <v>102.1320466035278</v>
+        <v>102.2325498826935</v>
       </c>
       <c r="O24" t="n">
-        <v>10.10604010498315</v>
+        <v>10.111011318493</v>
       </c>
       <c r="P24" t="n">
-        <v>419.3495658070362</v>
+        <v>419.2694699509864</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -30293,28 +30417,28 @@
         <v>0.0417</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.472240547515089</v>
+        <v>-1.457844171203053</v>
       </c>
       <c r="J25" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K25" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6090189418068646</v>
+        <v>0.6032545631959408</v>
       </c>
       <c r="M25" t="n">
-        <v>7.659863407529609</v>
+        <v>7.705993589354601</v>
       </c>
       <c r="N25" t="n">
-        <v>91.54506056949242</v>
+        <v>92.48245327094075</v>
       </c>
       <c r="O25" t="n">
-        <v>9.567918298642208</v>
+        <v>9.616779776564542</v>
       </c>
       <c r="P25" t="n">
-        <v>417.4538992577578</v>
+        <v>417.3291807755232</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -30371,28 +30495,28 @@
         <v>0.0425</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.514506763623486</v>
+        <v>-1.498481757774818</v>
       </c>
       <c r="J26" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K26" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L26" t="n">
-        <v>0.5737759135918881</v>
+        <v>0.567420267962361</v>
       </c>
       <c r="M26" t="n">
-        <v>8.560177096897537</v>
+        <v>8.617096577774507</v>
       </c>
       <c r="N26" t="n">
-        <v>112.0961145724746</v>
+        <v>113.2635190508267</v>
       </c>
       <c r="O26" t="n">
-        <v>10.58754525716299</v>
+        <v>10.64253348835824</v>
       </c>
       <c r="P26" t="n">
-        <v>408.1001127639182</v>
+        <v>407.9612851614768</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -30449,28 +30573,28 @@
         <v>0.0428</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.190131922275723</v>
+        <v>-1.17574118933335</v>
       </c>
       <c r="J27" t="n">
+        <v>225</v>
+      </c>
+      <c r="K27" t="n">
         <v>224</v>
       </c>
-      <c r="K27" t="n">
-        <v>223</v>
-      </c>
       <c r="L27" t="n">
-        <v>0.4842091734820237</v>
+        <v>0.4772880063927872</v>
       </c>
       <c r="M27" t="n">
-        <v>7.982963467464637</v>
+        <v>8.024016601677443</v>
       </c>
       <c r="N27" t="n">
-        <v>99.58687583656835</v>
+        <v>100.4923839307154</v>
       </c>
       <c r="O27" t="n">
-        <v>9.979322413699657</v>
+        <v>10.02458896567412</v>
       </c>
       <c r="P27" t="n">
-        <v>394.1927903686517</v>
+        <v>394.0682202493778</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -30527,28 +30651,28 @@
         <v>0.0419</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.106260225391226</v>
+        <v>-1.088032574923216</v>
       </c>
       <c r="J28" t="n">
+        <v>225</v>
+      </c>
+      <c r="K28" t="n">
         <v>224</v>
       </c>
-      <c r="K28" t="n">
-        <v>223</v>
-      </c>
       <c r="L28" t="n">
-        <v>0.4654114503443553</v>
+        <v>0.4539181384932299</v>
       </c>
       <c r="M28" t="n">
-        <v>7.610318690193481</v>
+        <v>7.682616226850251</v>
       </c>
       <c r="N28" t="n">
-        <v>92.78301556384385</v>
+        <v>94.53480858646742</v>
       </c>
       <c r="O28" t="n">
-        <v>9.632394072287733</v>
+        <v>9.722901243274428</v>
       </c>
       <c r="P28" t="n">
-        <v>387.1371296889397</v>
+        <v>386.9793461624178</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -30605,28 +30729,28 @@
         <v>0.0419</v>
       </c>
       <c r="I29" t="n">
-        <v>-1.057707055141172</v>
+        <v>-1.038298424735008</v>
       </c>
       <c r="J29" t="n">
+        <v>225</v>
+      </c>
+      <c r="K29" t="n">
         <v>224</v>
       </c>
-      <c r="K29" t="n">
-        <v>223</v>
-      </c>
       <c r="L29" t="n">
-        <v>0.4026553158482125</v>
+        <v>0.3908854321716237</v>
       </c>
       <c r="M29" t="n">
-        <v>7.931498357028581</v>
+        <v>8.006029234366709</v>
       </c>
       <c r="N29" t="n">
-        <v>109.5452794591032</v>
+        <v>111.5120065780638</v>
       </c>
       <c r="O29" t="n">
-        <v>10.46638808085689</v>
+        <v>10.55992455361608</v>
       </c>
       <c r="P29" t="n">
-        <v>379.9985798317339</v>
+        <v>379.8305734199465</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -30683,28 +30807,28 @@
         <v>0.0426</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.8908592735726104</v>
+        <v>-0.8710730638678899</v>
       </c>
       <c r="J30" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K30" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L30" t="n">
-        <v>0.3152373446620396</v>
+        <v>0.3030622781656925</v>
       </c>
       <c r="M30" t="n">
-        <v>7.985109085221792</v>
+        <v>8.050600663524277</v>
       </c>
       <c r="N30" t="n">
-        <v>113.4156710949359</v>
+        <v>115.4508311704808</v>
       </c>
       <c r="O30" t="n">
-        <v>10.64967938930257</v>
+        <v>10.74480484562101</v>
       </c>
       <c r="P30" t="n">
-        <v>374.4016807884126</v>
+        <v>374.2302691782922</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -30761,28 +30885,28 @@
         <v>0.0438</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8907521108670534</v>
+        <v>-0.8720415071895055</v>
       </c>
       <c r="J31" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K31" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L31" t="n">
-        <v>0.3333790189850419</v>
+        <v>0.3214777369981636</v>
       </c>
       <c r="M31" t="n">
-        <v>7.961624267104546</v>
+        <v>8.026840043442265</v>
       </c>
       <c r="N31" t="n">
-        <v>104.7979663221402</v>
+        <v>106.6165862555198</v>
       </c>
       <c r="O31" t="n">
-        <v>10.23708778521217</v>
+        <v>10.32553079776143</v>
       </c>
       <c r="P31" t="n">
-        <v>375.701225607954</v>
+        <v>375.5389683790094</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -30839,28 +30963,28 @@
         <v>0.0533</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.7208051613978017</v>
+        <v>-0.7074130952114762</v>
       </c>
       <c r="J32" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K32" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L32" t="n">
-        <v>0.3490124130519147</v>
+        <v>0.3387055161213378</v>
       </c>
       <c r="M32" t="n">
-        <v>6.223211280946244</v>
+        <v>6.265914666150612</v>
       </c>
       <c r="N32" t="n">
-        <v>64.18804742495881</v>
+        <v>65.07686430539997</v>
       </c>
       <c r="O32" t="n">
-        <v>8.01174434345972</v>
+        <v>8.067023261736635</v>
       </c>
       <c r="P32" t="n">
-        <v>352.1963285691994</v>
+        <v>352.0802196445717</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -30917,28 +31041,28 @@
         <v>0.0528</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.5516037200993191</v>
+        <v>-0.53832587010795</v>
       </c>
       <c r="J33" t="n">
+        <v>225</v>
+      </c>
+      <c r="K33" t="n">
         <v>224</v>
       </c>
-      <c r="K33" t="n">
-        <v>223</v>
-      </c>
       <c r="L33" t="n">
-        <v>0.2277361943808596</v>
+        <v>0.2181376855652832</v>
       </c>
       <c r="M33" t="n">
-        <v>6.253904193035149</v>
+        <v>6.302969780535455</v>
       </c>
       <c r="N33" t="n">
-        <v>68.06614169155635</v>
+        <v>68.91111815403941</v>
       </c>
       <c r="O33" t="n">
-        <v>8.250220705626992</v>
+        <v>8.301272080472932</v>
       </c>
       <c r="P33" t="n">
-        <v>337.4169221937632</v>
+        <v>337.3019201441278</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -30995,28 +31119,28 @@
         <v>0.0456</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6344261974067031</v>
+        <v>-0.6189836006838479</v>
       </c>
       <c r="J34" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K34" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L34" t="n">
-        <v>0.162927697307949</v>
+        <v>0.1561515578331059</v>
       </c>
       <c r="M34" t="n">
-        <v>8.648158155271796</v>
+        <v>8.712401298243581</v>
       </c>
       <c r="N34" t="n">
-        <v>137.0292676380919</v>
+        <v>137.9764033160421</v>
       </c>
       <c r="O34" t="n">
-        <v>11.70595009548956</v>
+        <v>11.74633573996768</v>
       </c>
       <c r="P34" t="n">
-        <v>331.566197218812</v>
+        <v>331.4327929906514</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -31073,28 +31197,28 @@
         <v>0.0526</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1713070136435563</v>
+        <v>-0.1644556362855568</v>
       </c>
       <c r="J35" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K35" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L35" t="n">
-        <v>0.007428124036339634</v>
+        <v>0.006910747813445361</v>
       </c>
       <c r="M35" t="n">
-        <v>13.0338935542539</v>
+        <v>13.00998890316247</v>
       </c>
       <c r="N35" t="n">
-        <v>260.7471206531879</v>
+        <v>259.8816040945539</v>
       </c>
       <c r="O35" t="n">
-        <v>16.14766610545276</v>
+        <v>16.12084377737574</v>
       </c>
       <c r="P35" t="n">
-        <v>306.0439574305064</v>
+        <v>305.9848308815405</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
@@ -31132,7 +31256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ225"/>
+  <dimension ref="A1:AJ226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71901,6 +72025,188 @@
         </is>
       </c>
     </row>
+    <row r="226">
+      <c r="A226" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>-34.50669269612864,172.7023034163352</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>-34.50590879745866,172.7024100728692</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>-34.50519291293844,172.70218087080127</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>-34.50450134547001,172.7018315712302</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>-34.503800113627435,172.70152611808905</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>-34.50314405064849,172.70111915212277</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>-34.50253401664471,172.70064356027854</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>-34.50192278306542,172.7001362840193</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>-34.501354668195596,172.6995563114221</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>-34.5007656438828,172.6990115804344</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>-34.50015991238256,172.6984950069703</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>-34.49953353460585,172.69801323145762</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>-34.49894953954069,172.69746000036216</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>-34.49836165323872,172.69691332176785</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>-34.4978014781114,172.69632591045777</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>-34.497254377288805,172.69572653733556</t>
+        </is>
+      </c>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t>-34.49669233638397,172.69514553082706</t>
+        </is>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>-34.49611396670843,172.69458472072895</t>
+        </is>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>-34.49553029331241,172.69403190158584</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>-34.49495507300203,172.69346633084817</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>-34.49438170922684,172.69289795480663</t>
+        </is>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>-34.49382085769793,172.69231070672063</t>
+        </is>
+      </c>
+      <c r="X226" t="inlineStr">
+        <is>
+          <t>-34.49328735461781,172.69172265969874</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>-34.49278051349488,172.69111263507605</t>
+        </is>
+      </c>
+      <c r="Z226" t="inlineStr">
+        <is>
+          <t>-34.4922345532236,172.69050668603515</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>-34.49169316623554,172.68988870594282</t>
+        </is>
+      </c>
+      <c r="AB226" t="inlineStr">
+        <is>
+          <t>-34.49120011858997,172.6892185359673</t>
+        </is>
+      </c>
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t>-34.49067842609431,172.68857928781216</t>
+        </is>
+      </c>
+      <c r="AD226" t="inlineStr">
+        <is>
+          <t>-34.490181839290884,172.68791375697728</t>
+        </is>
+      </c>
+      <c r="AE226" t="inlineStr">
+        <is>
+          <t>-34.489707133567656,172.68725206209095</t>
+        </is>
+      </c>
+      <c r="AF226" t="inlineStr">
+        <is>
+          <t>-34.48922236775617,172.68654243275523</t>
+        </is>
+      </c>
+      <c r="AG226" t="inlineStr">
+        <is>
+          <t>-34.488855240272024,172.6857541202514</t>
+        </is>
+      </c>
+      <c r="AH226" t="inlineStr">
+        <is>
+          <t>-34.488530311271056,172.68494483864362</t>
+        </is>
+      </c>
+      <c r="AI226" t="inlineStr">
+        <is>
+          <t>-34.48805184730376,172.68421185336064</t>
+        </is>
+      </c>
+      <c r="AJ226" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0008/nzd0008.xlsx
+++ b/data/nzd0008/nzd0008.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ226"/>
+  <dimension ref="A1:AJ228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26166,6 +26166,234 @@
         <v>309.88</v>
       </c>
       <c r="AJ226" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>368.45</v>
+      </c>
+      <c r="C227" t="n">
+        <v>337.37</v>
+      </c>
+      <c r="D227" t="n">
+        <v>338.14</v>
+      </c>
+      <c r="E227" t="n">
+        <v>350.09</v>
+      </c>
+      <c r="F227" t="n">
+        <v>359.21</v>
+      </c>
+      <c r="G227" t="n">
+        <v>376.06</v>
+      </c>
+      <c r="H227" t="n">
+        <v>369.98</v>
+      </c>
+      <c r="I227" t="n">
+        <v>369.95</v>
+      </c>
+      <c r="J227" t="n">
+        <v>374.22</v>
+      </c>
+      <c r="K227" t="n">
+        <v>376.33</v>
+      </c>
+      <c r="L227" t="n">
+        <v>375.56</v>
+      </c>
+      <c r="M227" t="n">
+        <v>372.25</v>
+      </c>
+      <c r="N227" t="n">
+        <v>374.66</v>
+      </c>
+      <c r="O227" t="n">
+        <v>376.5</v>
+      </c>
+      <c r="P227" t="n">
+        <v>382.5</v>
+      </c>
+      <c r="Q227" t="n">
+        <v>387.98</v>
+      </c>
+      <c r="R227" t="n">
+        <v>388.65</v>
+      </c>
+      <c r="S227" t="n">
+        <v>388.76</v>
+      </c>
+      <c r="T227" t="n">
+        <v>389.52</v>
+      </c>
+      <c r="U227" t="n">
+        <v>390.33</v>
+      </c>
+      <c r="V227" t="n">
+        <v>389.67</v>
+      </c>
+      <c r="W227" t="n">
+        <v>392.39</v>
+      </c>
+      <c r="X227" t="n">
+        <v>398.57</v>
+      </c>
+      <c r="Y227" t="n">
+        <v>397.92</v>
+      </c>
+      <c r="Z227" t="n">
+        <v>391.24</v>
+      </c>
+      <c r="AA227" t="n">
+        <v>383.56</v>
+      </c>
+      <c r="AB227" t="n">
+        <v>381.95</v>
+      </c>
+      <c r="AC227" t="n">
+        <v>376.58</v>
+      </c>
+      <c r="AD227" t="n">
+        <v>372.88</v>
+      </c>
+      <c r="AE227" t="n">
+        <v>371.07</v>
+      </c>
+      <c r="AF227" t="n">
+        <v>346.32</v>
+      </c>
+      <c r="AG227" t="n">
+        <v>336.81</v>
+      </c>
+      <c r="AH227" t="n">
+        <v>334.38</v>
+      </c>
+      <c r="AI227" t="n">
+        <v>313.54</v>
+      </c>
+      <c r="AJ227" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>367.44</v>
+      </c>
+      <c r="C228" t="n">
+        <v>337.44</v>
+      </c>
+      <c r="D228" t="n">
+        <v>337.7</v>
+      </c>
+      <c r="E228" t="n">
+        <v>349.68</v>
+      </c>
+      <c r="F228" t="n">
+        <v>359.67</v>
+      </c>
+      <c r="G228" t="n">
+        <v>377.54</v>
+      </c>
+      <c r="H228" t="n">
+        <v>371.46</v>
+      </c>
+      <c r="I228" t="n">
+        <v>371.24</v>
+      </c>
+      <c r="J228" t="n">
+        <v>374.63</v>
+      </c>
+      <c r="K228" t="n">
+        <v>376.19</v>
+      </c>
+      <c r="L228" t="n">
+        <v>375.9</v>
+      </c>
+      <c r="M228" t="n">
+        <v>372.85</v>
+      </c>
+      <c r="N228" t="n">
+        <v>375.75</v>
+      </c>
+      <c r="O228" t="n">
+        <v>377.82</v>
+      </c>
+      <c r="P228" t="n">
+        <v>383.99</v>
+      </c>
+      <c r="Q228" t="n">
+        <v>387.97</v>
+      </c>
+      <c r="R228" t="n">
+        <v>388.6</v>
+      </c>
+      <c r="S228" t="n">
+        <v>388.42</v>
+      </c>
+      <c r="T228" t="n">
+        <v>389.93</v>
+      </c>
+      <c r="U228" t="n">
+        <v>389.83</v>
+      </c>
+      <c r="V228" t="n">
+        <v>388.75</v>
+      </c>
+      <c r="W228" t="n">
+        <v>391.75</v>
+      </c>
+      <c r="X228" t="n">
+        <v>399.37</v>
+      </c>
+      <c r="Y228" t="n">
+        <v>399.7</v>
+      </c>
+      <c r="Z228" t="n">
+        <v>393.53</v>
+      </c>
+      <c r="AA228" t="n">
+        <v>386.05</v>
+      </c>
+      <c r="AB228" t="n">
+        <v>383.2</v>
+      </c>
+      <c r="AC228" t="n">
+        <v>376.09</v>
+      </c>
+      <c r="AD228" t="n">
+        <v>371.5</v>
+      </c>
+      <c r="AE228" t="n">
+        <v>368.75</v>
+      </c>
+      <c r="AF228" t="n">
+        <v>342.95</v>
+      </c>
+      <c r="AG228" t="n">
+        <v>335.48</v>
+      </c>
+      <c r="AH228" t="n">
+        <v>333.12</v>
+      </c>
+      <c r="AI228" t="n">
+        <v>311.78</v>
+      </c>
+      <c r="AJ228" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -26182,7 +26410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B227"/>
+  <dimension ref="A1:B229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28455,6 +28683,26 @@
       </c>
       <c r="B227" t="n">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>0.62</v>
       </c>
     </row>
   </sheetData>
@@ -28623,28 +28871,28 @@
         <v>0.0307</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2394711759192466</v>
+        <v>-0.2419788141046113</v>
       </c>
       <c r="J2" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K2" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02835934058278999</v>
+        <v>0.02950033220405268</v>
       </c>
       <c r="M2" t="n">
-        <v>8.222176251851536</v>
+        <v>8.164460018155504</v>
       </c>
       <c r="N2" t="n">
-        <v>129.7482439220466</v>
+        <v>128.6230721082566</v>
       </c>
       <c r="O2" t="n">
-        <v>11.39070866636693</v>
+        <v>11.34121122756545</v>
       </c>
       <c r="P2" t="n">
-        <v>375.8151133880185</v>
+        <v>375.837013240507</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28701,28 +28949,28 @@
         <v>0.0407</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3684938734765952</v>
+        <v>-0.3838996914555645</v>
       </c>
       <c r="J3" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K3" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1149412288969532</v>
+        <v>0.1244715947558163</v>
       </c>
       <c r="M3" t="n">
-        <v>6.349058146943312</v>
+        <v>6.372884711462365</v>
       </c>
       <c r="N3" t="n">
-        <v>69.18032935226499</v>
+        <v>69.35771138101897</v>
       </c>
       <c r="O3" t="n">
-        <v>8.317471331616659</v>
+        <v>8.328127723625459</v>
       </c>
       <c r="P3" t="n">
-        <v>356.7142771645394</v>
+        <v>356.848259186536</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28779,28 +29027,28 @@
         <v>0.0421</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3110983642388629</v>
+        <v>-0.3169322468048976</v>
       </c>
       <c r="J4" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K4" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1010443731319896</v>
+        <v>0.1061636976171818</v>
       </c>
       <c r="M4" t="n">
-        <v>6.089185932666729</v>
+        <v>6.067003850660877</v>
       </c>
       <c r="N4" t="n">
-        <v>56.97015274976256</v>
+        <v>56.58144740698751</v>
       </c>
       <c r="O4" t="n">
-        <v>7.547857494002027</v>
+        <v>7.522064039011335</v>
       </c>
       <c r="P4" t="n">
-        <v>349.7615930735997</v>
+        <v>349.8123312665841</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28857,28 +29105,28 @@
         <v>0.0379</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2445653193781027</v>
+        <v>-0.2389335544741008</v>
       </c>
       <c r="J5" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K5" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0714456021551545</v>
+        <v>0.06956598035704065</v>
       </c>
       <c r="M5" t="n">
-        <v>5.765292029108084</v>
+        <v>5.741322247286091</v>
       </c>
       <c r="N5" t="n">
-        <v>51.43365667841572</v>
+        <v>51.08603544275972</v>
       </c>
       <c r="O5" t="n">
-        <v>7.171726199348084</v>
+        <v>7.147449576090741</v>
       </c>
       <c r="P5" t="n">
-        <v>352.8331566860114</v>
+        <v>352.7841796121837</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28935,28 +29183,28 @@
         <v>0.0309</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3153991979211125</v>
+        <v>-0.3033486751561238</v>
       </c>
       <c r="J6" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K6" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08839948088104876</v>
+        <v>0.08329426961015207</v>
       </c>
       <c r="M6" t="n">
-        <v>6.528050036979137</v>
+        <v>6.530510069071235</v>
       </c>
       <c r="N6" t="n">
-        <v>67.87374707814666</v>
+        <v>67.7576395339716</v>
       </c>
       <c r="O6" t="n">
-        <v>8.23855248682356</v>
+        <v>8.231502872135295</v>
       </c>
       <c r="P6" t="n">
-        <v>360.2615205560079</v>
+        <v>360.1567169469363</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29013,28 +29261,28 @@
         <v>0.0305</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1809706969265717</v>
+        <v>-0.1631582449067747</v>
       </c>
       <c r="J7" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K7" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01818101333771716</v>
+        <v>0.01498882973899229</v>
       </c>
       <c r="M7" t="n">
-        <v>8.665035357220065</v>
+        <v>8.683447950464785</v>
       </c>
       <c r="N7" t="n">
-        <v>117.0188069993177</v>
+        <v>117.0444217098093</v>
       </c>
       <c r="O7" t="n">
-        <v>10.81752314531001</v>
+        <v>10.81870702578683</v>
       </c>
       <c r="P7" t="n">
-        <v>370.4879439111825</v>
+        <v>370.3330255721532</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29091,28 +29339,28 @@
         <v>0.0362</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2021343633129424</v>
+        <v>-0.1877099442741701</v>
       </c>
       <c r="J8" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K8" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03299030327791741</v>
+        <v>0.02889152520157123</v>
       </c>
       <c r="M8" t="n">
-        <v>7.233007495656977</v>
+        <v>7.262837067907745</v>
       </c>
       <c r="N8" t="n">
-        <v>79.24112455526445</v>
+        <v>79.23755710534266</v>
       </c>
       <c r="O8" t="n">
-        <v>8.901748398784614</v>
+        <v>8.901548017358703</v>
       </c>
       <c r="P8" t="n">
-        <v>367.0781297342909</v>
+        <v>366.9526766243317</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29169,28 +29417,28 @@
         <v>0.0308</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4562992801607044</v>
+        <v>-0.4316303217461778</v>
       </c>
       <c r="J9" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K9" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09245879240163757</v>
+        <v>0.08392892758589987</v>
       </c>
       <c r="M9" t="n">
-        <v>9.315230429805231</v>
+        <v>9.373133801322917</v>
       </c>
       <c r="N9" t="n">
-        <v>135.2208032905745</v>
+        <v>136.050652343418</v>
       </c>
       <c r="O9" t="n">
-        <v>11.62844801727963</v>
+        <v>11.66407528882671</v>
       </c>
       <c r="P9" t="n">
-        <v>367.2822618979814</v>
+        <v>367.0677141351028</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29247,28 +29495,28 @@
         <v>0.0363</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5829977812198223</v>
+        <v>-0.5608736194260644</v>
       </c>
       <c r="J10" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K10" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1650172250318577</v>
+        <v>0.1553756045625464</v>
       </c>
       <c r="M10" t="n">
-        <v>8.89327919263175</v>
+        <v>8.938964003973989</v>
       </c>
       <c r="N10" t="n">
-        <v>113.7909827275296</v>
+        <v>114.4115996725622</v>
       </c>
       <c r="O10" t="n">
-        <v>10.6672856307277</v>
+        <v>10.69633580589924</v>
       </c>
       <c r="P10" t="n">
-        <v>376.0370359790526</v>
+        <v>375.8446234552468</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29325,28 +29573,28 @@
         <v>0.0417</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6708948087955292</v>
+        <v>-0.649739681596524</v>
       </c>
       <c r="J11" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K11" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1984451343462083</v>
+        <v>0.1896124392192213</v>
       </c>
       <c r="M11" t="n">
-        <v>8.883552898185476</v>
+        <v>8.918710894020579</v>
       </c>
       <c r="N11" t="n">
-        <v>120.820653572112</v>
+        <v>121.2426498171087</v>
       </c>
       <c r="O11" t="n">
-        <v>10.99184486663235</v>
+        <v>11.01102401310199</v>
       </c>
       <c r="P11" t="n">
-        <v>380.791112401272</v>
+        <v>380.6075870740978</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -29403,28 +29651,28 @@
         <v>0.035</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.73014179504886</v>
+        <v>-0.7111219482916334</v>
       </c>
       <c r="J12" t="n">
+        <v>227</v>
+      </c>
+      <c r="K12" t="n">
         <v>225</v>
       </c>
-      <c r="K12" t="n">
-        <v>223</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.195699983886046</v>
+        <v>0.1892909506780898</v>
       </c>
       <c r="M12" t="n">
-        <v>9.565373174688835</v>
+        <v>9.579538639066909</v>
       </c>
       <c r="N12" t="n">
-        <v>145.5388589378433</v>
+        <v>145.4540944739117</v>
       </c>
       <c r="O12" t="n">
-        <v>12.06394872907885</v>
+        <v>12.06043508642668</v>
       </c>
       <c r="P12" t="n">
-        <v>383.1636676025623</v>
+        <v>382.9980783795509</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -29481,28 +29729,28 @@
         <v>0.0377</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.9438538518569726</v>
+        <v>-0.9313239656004585</v>
       </c>
       <c r="J13" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K13" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2743216583407561</v>
+        <v>0.2722851080234678</v>
       </c>
       <c r="M13" t="n">
-        <v>10.22159737858781</v>
+        <v>10.19732732647805</v>
       </c>
       <c r="N13" t="n">
-        <v>156.9644732890229</v>
+        <v>156.0908158782347</v>
       </c>
       <c r="O13" t="n">
-        <v>12.52854633582935</v>
+        <v>12.49363101256935</v>
       </c>
       <c r="P13" t="n">
-        <v>389.6550961915793</v>
+        <v>389.5460296224916</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -29559,28 +29807,28 @@
         <v>0.0472</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.89254183713792</v>
+        <v>-0.8843801190250092</v>
       </c>
       <c r="J14" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K14" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3227058128922525</v>
+        <v>0.3225833689809493</v>
       </c>
       <c r="M14" t="n">
-        <v>8.460006966818057</v>
+        <v>8.425434240925924</v>
       </c>
       <c r="N14" t="n">
-        <v>111.3616155805094</v>
+        <v>110.5936632140741</v>
       </c>
       <c r="O14" t="n">
-        <v>10.55280131436717</v>
+        <v>10.51635218191527</v>
       </c>
       <c r="P14" t="n">
-        <v>393.6754928767524</v>
+        <v>393.6044462051819</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -29637,28 +29885,28 @@
         <v>0.0445</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.039153984687942</v>
+        <v>-1.030006981712206</v>
       </c>
       <c r="J15" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K15" t="n">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3781809471982265</v>
+        <v>0.3781428513550005</v>
       </c>
       <c r="M15" t="n">
-        <v>8.701800331619735</v>
+        <v>8.675874004903314</v>
       </c>
       <c r="N15" t="n">
-        <v>117.4136530014635</v>
+        <v>116.6328308059092</v>
       </c>
       <c r="O15" t="n">
-        <v>10.83575807230225</v>
+        <v>10.7996680877659</v>
       </c>
       <c r="P15" t="n">
-        <v>398.952527965597</v>
+        <v>398.8720325143843</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -29715,28 +29963,28 @@
         <v>0.0452</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9465833356186497</v>
+        <v>-0.9362969077893059</v>
       </c>
       <c r="J16" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K16" t="n">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3433460121722939</v>
+        <v>0.3422013359740046</v>
       </c>
       <c r="M16" t="n">
-        <v>8.639994550536398</v>
+        <v>8.622429338318007</v>
       </c>
       <c r="N16" t="n">
-        <v>113.32264262972</v>
+        <v>112.6533750569677</v>
       </c>
       <c r="O16" t="n">
-        <v>10.64531082823419</v>
+        <v>10.61382942471602</v>
       </c>
       <c r="P16" t="n">
-        <v>401.8957989940356</v>
+        <v>401.8052763967564</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -29793,28 +30041,28 @@
         <v>0.0472</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9383223462115223</v>
+        <v>-0.9252599384291673</v>
       </c>
       <c r="J17" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K17" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3616944600045779</v>
+        <v>0.3585318710452486</v>
       </c>
       <c r="M17" t="n">
-        <v>8.154867257306432</v>
+        <v>8.158601898912522</v>
       </c>
       <c r="N17" t="n">
-        <v>103.0825077561277</v>
+        <v>102.7280115748581</v>
       </c>
       <c r="O17" t="n">
-        <v>10.15295561677129</v>
+        <v>10.13548279929763</v>
       </c>
       <c r="P17" t="n">
-        <v>404.6410120034035</v>
+        <v>404.5266954943623</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -29871,28 +30119,28 @@
         <v>0.0468</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.033591590868032</v>
+        <v>-1.01987827856637</v>
       </c>
       <c r="J18" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K18" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3881750131359483</v>
+        <v>0.3852118343105725</v>
       </c>
       <c r="M18" t="n">
-        <v>8.538209126435287</v>
+        <v>8.542628104327912</v>
       </c>
       <c r="N18" t="n">
-        <v>111.709901227416</v>
+        <v>111.3362555975087</v>
       </c>
       <c r="O18" t="n">
-        <v>10.56929047890236</v>
+        <v>10.55159967007414</v>
       </c>
       <c r="P18" t="n">
-        <v>407.4030088197276</v>
+        <v>407.2829960489999</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -29949,28 +30197,28 @@
         <v>0.0452</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.079138721742054</v>
+        <v>-1.065127674843112</v>
       </c>
       <c r="J19" t="n">
+        <v>227</v>
+      </c>
+      <c r="K19" t="n">
         <v>225</v>
       </c>
-      <c r="K19" t="n">
-        <v>223</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.4150408482412825</v>
+        <v>0.4120763890953419</v>
       </c>
       <c r="M19" t="n">
-        <v>8.582900235158407</v>
+        <v>8.581819180601071</v>
       </c>
       <c r="N19" t="n">
-        <v>108.1524107256425</v>
+        <v>107.8402936961002</v>
       </c>
       <c r="O19" t="n">
-        <v>10.39963512463983</v>
+        <v>10.38461812952697</v>
       </c>
       <c r="P19" t="n">
-        <v>408.3912078863675</v>
+        <v>408.2683590841943</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -30027,28 +30275,28 @@
         <v>0.0417</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9941769433671618</v>
+        <v>-0.9793070236727595</v>
       </c>
       <c r="J20" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K20" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3141047303955414</v>
+        <v>0.3108115417889303</v>
       </c>
       <c r="M20" t="n">
-        <v>9.820149378463856</v>
+        <v>9.807397790207007</v>
       </c>
       <c r="N20" t="n">
-        <v>142.8027306699341</v>
+        <v>142.2780282289125</v>
       </c>
       <c r="O20" t="n">
-        <v>11.95000965145778</v>
+        <v>11.92803538848341</v>
       </c>
       <c r="P20" t="n">
-        <v>406.6954597729112</v>
+        <v>406.5661363745964</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -30105,28 +30353,28 @@
         <v>0.0364</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.366604897081647</v>
+        <v>-1.349183565086036</v>
       </c>
       <c r="J21" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K21" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4943036005474023</v>
+        <v>0.4908835459751011</v>
       </c>
       <c r="M21" t="n">
-        <v>9.202094973952974</v>
+        <v>9.230046203577004</v>
       </c>
       <c r="N21" t="n">
-        <v>126.4176870981549</v>
+        <v>126.3106539564891</v>
       </c>
       <c r="O21" t="n">
-        <v>11.24356202891926</v>
+        <v>11.23880126866247</v>
       </c>
       <c r="P21" t="n">
-        <v>415.2936849102621</v>
+        <v>415.1421758108444</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -30183,28 +30431,28 @@
         <v>0.041</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.415629265498546</v>
+        <v>-1.403230439782291</v>
       </c>
       <c r="J22" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K22" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5790635872458905</v>
+        <v>0.5783432044451867</v>
       </c>
       <c r="M22" t="n">
-        <v>8.10653115492085</v>
+        <v>8.114962099350651</v>
       </c>
       <c r="N22" t="n">
-        <v>96.38625606866516</v>
+        <v>96.04852555605429</v>
       </c>
       <c r="O22" t="n">
-        <v>9.817650231530209</v>
+        <v>9.800434967696805</v>
       </c>
       <c r="P22" t="n">
-        <v>418.840341902899</v>
+        <v>418.7325145110109</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -30261,28 +30509,28 @@
         <v>0.0413</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.178540889180409</v>
+        <v>-1.169210094651611</v>
       </c>
       <c r="J23" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K23" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5233071460921315</v>
+        <v>0.5234564652018572</v>
       </c>
       <c r="M23" t="n">
-        <v>7.521332530885607</v>
+        <v>7.511625708729269</v>
       </c>
       <c r="N23" t="n">
-        <v>83.71380715989123</v>
+        <v>83.26574410948695</v>
       </c>
       <c r="O23" t="n">
-        <v>9.149524969083981</v>
+        <v>9.125006526544896</v>
       </c>
       <c r="P23" t="n">
-        <v>417.3577563720414</v>
+        <v>417.2766101252432</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -30339,28 +30587,28 @@
         <v>0.0373</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.193864673311333</v>
+        <v>-1.175879483608329</v>
       </c>
       <c r="J24" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K24" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4798327133624916</v>
+        <v>0.4746132798689997</v>
       </c>
       <c r="M24" t="n">
-        <v>8.242415598067087</v>
+        <v>8.261687007816455</v>
       </c>
       <c r="N24" t="n">
-        <v>102.2325498826935</v>
+        <v>102.4056863247017</v>
       </c>
       <c r="O24" t="n">
-        <v>10.111011318493</v>
+        <v>10.11956947328797</v>
       </c>
       <c r="P24" t="n">
-        <v>419.2694699509864</v>
+        <v>419.1130519145306</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -30417,28 +30665,28 @@
         <v>0.0417</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.457844171203053</v>
+        <v>-1.425798002504492</v>
       </c>
       <c r="J25" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K25" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6032545631959408</v>
+        <v>0.5885625461288887</v>
       </c>
       <c r="M25" t="n">
-        <v>7.705993589354601</v>
+        <v>7.821047300750982</v>
       </c>
       <c r="N25" t="n">
-        <v>92.48245327094075</v>
+        <v>95.079403186088</v>
       </c>
       <c r="O25" t="n">
-        <v>9.616779776564542</v>
+        <v>9.750866791526176</v>
       </c>
       <c r="P25" t="n">
-        <v>417.3291807755232</v>
+        <v>417.0504723930123</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -30495,28 +30743,28 @@
         <v>0.0425</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.498481757774818</v>
+        <v>-1.459982771132087</v>
       </c>
       <c r="J26" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K26" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L26" t="n">
-        <v>0.567420267962361</v>
+        <v>0.5489225035979566</v>
       </c>
       <c r="M26" t="n">
-        <v>8.617096577774507</v>
+        <v>8.770539981478802</v>
       </c>
       <c r="N26" t="n">
-        <v>113.2635190508267</v>
+        <v>117.1911534114351</v>
       </c>
       <c r="O26" t="n">
-        <v>10.64253348835824</v>
+        <v>10.82548628983636</v>
       </c>
       <c r="P26" t="n">
-        <v>407.9612851614768</v>
+        <v>407.6264554565062</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -30573,28 +30821,28 @@
         <v>0.0428</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.17574118933335</v>
+        <v>-1.140791708216316</v>
       </c>
       <c r="J27" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K27" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L27" t="n">
-        <v>0.4772880063927872</v>
+        <v>0.4572287561614815</v>
       </c>
       <c r="M27" t="n">
-        <v>8.024016601677443</v>
+        <v>8.140501189572278</v>
       </c>
       <c r="N27" t="n">
-        <v>100.4923839307154</v>
+        <v>103.6868627082791</v>
       </c>
       <c r="O27" t="n">
-        <v>10.02458896567412</v>
+        <v>10.18267463431289</v>
       </c>
       <c r="P27" t="n">
-        <v>394.0682202493778</v>
+        <v>393.7644934235408</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -30651,28 +30899,28 @@
         <v>0.0419</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.088032574923216</v>
+        <v>-1.048997989777639</v>
       </c>
       <c r="J28" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K28" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L28" t="n">
-        <v>0.4539181384932299</v>
+        <v>0.4278112065512913</v>
       </c>
       <c r="M28" t="n">
-        <v>7.682616226850251</v>
+        <v>7.844443018495022</v>
       </c>
       <c r="N28" t="n">
-        <v>94.53480858646742</v>
+        <v>98.77891032547804</v>
       </c>
       <c r="O28" t="n">
-        <v>9.722901243274428</v>
+        <v>9.938757987066495</v>
       </c>
       <c r="P28" t="n">
-        <v>386.9793461624178</v>
+        <v>386.640124031278</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -30729,28 +30977,28 @@
         <v>0.0419</v>
       </c>
       <c r="I29" t="n">
-        <v>-1.038298424735008</v>
+        <v>-0.9999199721748318</v>
       </c>
       <c r="J29" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K29" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3908854321716237</v>
+        <v>0.3676222035066221</v>
       </c>
       <c r="M29" t="n">
-        <v>8.006029234366709</v>
+        <v>8.157014283377228</v>
       </c>
       <c r="N29" t="n">
-        <v>111.5120065780638</v>
+        <v>115.4338267322583</v>
       </c>
       <c r="O29" t="n">
-        <v>10.55992455361608</v>
+        <v>10.74401352997372</v>
       </c>
       <c r="P29" t="n">
-        <v>379.8305734199465</v>
+        <v>379.4970601306958</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -30807,28 +31055,28 @@
         <v>0.0426</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.8710730638678899</v>
+        <v>-0.8374213323236682</v>
       </c>
       <c r="J30" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K30" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L30" t="n">
-        <v>0.3030622781656925</v>
+        <v>0.2841648996837463</v>
       </c>
       <c r="M30" t="n">
-        <v>8.050600663524277</v>
+        <v>8.16176755942038</v>
       </c>
       <c r="N30" t="n">
-        <v>115.4508311704808</v>
+        <v>118.1924780346797</v>
       </c>
       <c r="O30" t="n">
-        <v>10.74480484562101</v>
+        <v>10.87163640096006</v>
       </c>
       <c r="P30" t="n">
-        <v>374.2302691782922</v>
+        <v>373.9376099918913</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -30885,28 +31133,28 @@
         <v>0.0438</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8720415071895055</v>
+        <v>-0.8441031454747303</v>
       </c>
       <c r="J31" t="n">
+        <v>227</v>
+      </c>
+      <c r="K31" t="n">
         <v>225</v>
       </c>
-      <c r="K31" t="n">
-        <v>223</v>
-      </c>
       <c r="L31" t="n">
-        <v>0.3214777369981636</v>
+        <v>0.3064634978578257</v>
       </c>
       <c r="M31" t="n">
-        <v>8.026840043442265</v>
+        <v>8.110080436056034</v>
       </c>
       <c r="N31" t="n">
-        <v>106.6165862555198</v>
+        <v>108.2889701240132</v>
       </c>
       <c r="O31" t="n">
-        <v>10.32553079776143</v>
+        <v>10.40619863946548</v>
       </c>
       <c r="P31" t="n">
-        <v>375.5389683790094</v>
+        <v>375.2957447539004</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -30963,28 +31211,28 @@
         <v>0.0533</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.7074130952114762</v>
+        <v>-0.6893750251097155</v>
       </c>
       <c r="J32" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K32" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L32" t="n">
-        <v>0.3387055161213378</v>
+        <v>0.3278236352729524</v>
       </c>
       <c r="M32" t="n">
-        <v>6.265914666150612</v>
+        <v>6.304609110105472</v>
       </c>
       <c r="N32" t="n">
-        <v>65.07686430539997</v>
+        <v>65.6133915491112</v>
       </c>
       <c r="O32" t="n">
-        <v>8.067023261736635</v>
+        <v>8.100209352177954</v>
       </c>
       <c r="P32" t="n">
-        <v>352.0802196445717</v>
+        <v>351.9232241319363</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -31041,28 +31289,28 @@
         <v>0.0528</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.53832587010795</v>
+        <v>-0.5173684085783701</v>
       </c>
       <c r="J33" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K33" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2181376855652832</v>
+        <v>0.2046827750522155</v>
       </c>
       <c r="M33" t="n">
-        <v>6.302969780535455</v>
+        <v>6.372841228161033</v>
       </c>
       <c r="N33" t="n">
-        <v>68.91111815403941</v>
+        <v>69.76818672319516</v>
       </c>
       <c r="O33" t="n">
-        <v>8.301272080472932</v>
+        <v>8.352735283917189</v>
       </c>
       <c r="P33" t="n">
-        <v>337.3019201441278</v>
+        <v>337.1196983551562</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -31119,28 +31367,28 @@
         <v>0.0456</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6189836006838479</v>
+        <v>-0.5890288451823376</v>
       </c>
       <c r="J34" t="n">
+        <v>227</v>
+      </c>
+      <c r="K34" t="n">
         <v>225</v>
       </c>
-      <c r="K34" t="n">
-        <v>223</v>
-      </c>
       <c r="L34" t="n">
-        <v>0.1561515578331059</v>
+        <v>0.1432967728840469</v>
       </c>
       <c r="M34" t="n">
-        <v>8.712401298243581</v>
+        <v>8.836870106463925</v>
       </c>
       <c r="N34" t="n">
-        <v>137.9764033160421</v>
+        <v>139.7568881476679</v>
       </c>
       <c r="O34" t="n">
-        <v>11.74633573996768</v>
+        <v>11.82188175155157</v>
       </c>
       <c r="P34" t="n">
-        <v>331.4327929906514</v>
+        <v>331.1730069090494</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -31197,28 +31445,28 @@
         <v>0.0526</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1644556362855568</v>
+        <v>-0.1467755397888527</v>
       </c>
       <c r="J35" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K35" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L35" t="n">
-        <v>0.006910747813445361</v>
+        <v>0.005599707266067955</v>
       </c>
       <c r="M35" t="n">
-        <v>13.00998890316247</v>
+        <v>12.98401524480503</v>
       </c>
       <c r="N35" t="n">
-        <v>259.8816040945539</v>
+        <v>258.6200556467491</v>
       </c>
       <c r="O35" t="n">
-        <v>16.12084377737574</v>
+        <v>16.08166831043188</v>
       </c>
       <c r="P35" t="n">
-        <v>305.9848308815405</v>
+        <v>305.8316547926465</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
@@ -31256,7 +31504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ226"/>
+  <dimension ref="A1:AJ228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72207,6 +72455,370 @@
         </is>
       </c>
     </row>
+    <row r="227">
+      <c r="A227" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>-34.50669756081455,172.7022793961652</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>-34.50591229063048,172.70239282507518</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>-34.50519527027991,172.70216923128132</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>-34.504502202675965,172.70182733870985</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>-34.50380245835675,172.70151514885433</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>-34.50314850539283,172.70110783955042</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>-34.502532230781696,172.7006465708671</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>-34.50193144971488,172.70012167388234</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>-34.50135325002402,172.69955870216185</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>-34.50076370047191,172.69901485661836</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>-34.50015901946804,172.6984965122366</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>-34.499540993037876,172.69800065812365</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>-34.49895300611876,172.6974541564443</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>-34.49836202090432,172.69691270196122</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>-34.497795135824624,172.6963362312757</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>-34.49724363250568,172.69574307550772</t>
+        </is>
+      </c>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>-34.496672546717974,172.69517536971506</t>
+        </is>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>-34.496096601493804,172.69461090403416</t>
+        </is>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>-34.495524316998505,172.69404091268652</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>-34.49495231037868,172.69347049634038</t>
+        </is>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>-34.494372011897795,172.69291257647498</t>
+        </is>
+      </c>
+      <c r="W227" t="inlineStr">
+        <is>
+          <t>-34.49381076575759,172.6923259234009</t>
+        </is>
+      </c>
+      <c r="X227" t="inlineStr">
+        <is>
+          <t>-34.49328503643563,172.6917257078849</t>
+        </is>
+      </c>
+      <c r="Y227" t="inlineStr">
+        <is>
+          <t>-34.49279158677612,172.69110030673914</t>
+        </is>
+      </c>
+      <c r="Z227" t="inlineStr">
+        <is>
+          <t>-34.49225795112617,172.69048142582096</t>
+        </is>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>-34.491714412537135,172.6898657685608</t>
+        </is>
+      </c>
+      <c r="AB227" t="inlineStr">
+        <is>
+          <t>-34.49121168298958,172.6892060510792</t>
+        </is>
+      </c>
+      <c r="AC227" t="inlineStr">
+        <is>
+          <t>-34.49068367039695,172.68857362607147</t>
+        </is>
+      </c>
+      <c r="AD227" t="inlineStr">
+        <is>
+          <t>-34.49016717950194,172.6879294132227</t>
+        </is>
+      </c>
+      <c r="AE227" t="inlineStr">
+        <is>
+          <t>-34.48967677082962,172.68727476703214</t>
+        </is>
+      </c>
+      <c r="AF227" t="inlineStr">
+        <is>
+          <t>-34.489195680495996,172.6865556941038</t>
+        </is>
+      </c>
+      <c r="AG227" t="inlineStr">
+        <is>
+          <t>-34.48883639243225,172.68576348614891</t>
+        </is>
+      </c>
+      <c r="AH227" t="inlineStr">
+        <is>
+          <t>-34.48853614908517,172.68494193767668</t>
+        </is>
+      </c>
+      <c r="AI227" t="inlineStr">
+        <is>
+          <t>-34.48808237067789,172.6841966853719</t>
+        </is>
+      </c>
+      <c r="AJ227" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>-34.50669539635137,172.70229008355398</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>-34.50591244064395,172.70239208437232</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>-34.50519432734347,172.70217388708934</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>-34.50450132403987,172.7018316770432</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>-34.50380349544826,172.70151029707722</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>-34.50315423845357,172.70109328075986</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>-34.50254000453775,172.70063346595123</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>-34.50193822545777,172.70011025140948</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>-34.501355403543805,172.69955507177923</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>-34.50076296512724,172.69901609625555</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>-34.50016080529704,172.69849350170395</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>-34.49954414448763,172.69799534544666</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>-34.498958731224356,172.69744450512442</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>-34.498368954026226,172.6969010141777</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>-34.49780314430524,172.6963231990562</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>-34.49724357683323,172.69574316119773</t>
+        </is>
+      </c>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t>-34.496672264813846,172.69517579477034</t>
+        </is>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>-34.49609468455418,172.69461379439832</t>
+        </is>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>-34.495526628591705,172.69403742726092</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>-34.49494949137512,172.69347474684236</t>
+        </is>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>-34.494366824953616,172.692920397366</t>
+        </is>
+      </c>
+      <c r="W228" t="inlineStr">
+        <is>
+          <t>-34.493807157465596,172.69233136400072</t>
+        </is>
+      </c>
+      <c r="X228" t="inlineStr">
+        <is>
+          <t>-34.49328991681909,172.69171929065067</t>
+        </is>
+      </c>
+      <c r="Y228" t="inlineStr">
+        <is>
+          <t>-34.49280338943375,172.6910871663525</t>
+        </is>
+      </c>
+      <c r="Z228" t="inlineStr">
+        <is>
+          <t>-34.492273348018884,172.69046480343096</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>-34.49173115408176,172.68984769447627</t>
+        </is>
+      </c>
+      <c r="AB228" t="inlineStr">
+        <is>
+          <t>-34.49122008734895,172.68919697775715</t>
+        </is>
+      </c>
+      <c r="AC228" t="inlineStr">
+        <is>
+          <t>-34.49068037589917,172.68857718280609</t>
+        </is>
+      </c>
+      <c r="AD228" t="inlineStr">
+        <is>
+          <t>-34.490157856685784,172.68793936972608</t>
+        </is>
+      </c>
+      <c r="AE228" t="inlineStr">
+        <is>
+          <t>-34.48965898255678,172.6872880689092</t>
+        </is>
+      </c>
+      <c r="AF228" t="inlineStr">
+        <is>
+          <t>-34.48916757547338,172.68656965995228</t>
+        </is>
+      </c>
+      <c r="AG228" t="inlineStr">
+        <is>
+          <t>-34.488825300561565,172.68576899793615</t>
+        </is>
+      </c>
+      <c r="AH228" t="inlineStr">
+        <is>
+          <t>-34.4885256410197,172.68494715941688</t>
+        </is>
+      </c>
+      <c r="AI228" t="inlineStr">
+        <is>
+          <t>-34.488067692771466,172.6842039792695</t>
+        </is>
+      </c>
+      <c r="AJ228" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0008/nzd0008.xlsx
+++ b/data/nzd0008/nzd0008.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ228"/>
+  <dimension ref="A1:AJ229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26396,6 +26396,120 @@
       <c r="AJ228" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:17:45+00:00</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>364.5</v>
+      </c>
+      <c r="C229" t="n">
+        <v>339.67</v>
+      </c>
+      <c r="D229" t="n">
+        <v>337.54</v>
+      </c>
+      <c r="E229" t="n">
+        <v>348.16</v>
+      </c>
+      <c r="F229" t="n">
+        <v>356.93</v>
+      </c>
+      <c r="G229" t="n">
+        <v>374.66</v>
+      </c>
+      <c r="H229" t="n">
+        <v>369.98</v>
+      </c>
+      <c r="I229" t="n">
+        <v>365.56</v>
+      </c>
+      <c r="J229" t="n">
+        <v>371.54</v>
+      </c>
+      <c r="K229" t="n">
+        <v>370.25</v>
+      </c>
+      <c r="L229" t="n">
+        <v>371.02</v>
+      </c>
+      <c r="M229" t="n">
+        <v>368.74</v>
+      </c>
+      <c r="N229" t="n">
+        <v>376.5</v>
+      </c>
+      <c r="O229" t="n">
+        <v>380.22</v>
+      </c>
+      <c r="P229" t="n">
+        <v>383.13</v>
+      </c>
+      <c r="Q229" t="n">
+        <v>381.82</v>
+      </c>
+      <c r="R229" t="n">
+        <v>381.1</v>
+      </c>
+      <c r="S229" t="n">
+        <v>383.83</v>
+      </c>
+      <c r="T229" t="n">
+        <v>388.79</v>
+      </c>
+      <c r="U229" t="n">
+        <v>386.91</v>
+      </c>
+      <c r="V229" t="n">
+        <v>383.72</v>
+      </c>
+      <c r="W229" t="n">
+        <v>389.25</v>
+      </c>
+      <c r="X229" t="n">
+        <v>398.05</v>
+      </c>
+      <c r="Y229" t="n">
+        <v>398</v>
+      </c>
+      <c r="Z229" t="n">
+        <v>391.62</v>
+      </c>
+      <c r="AA229" t="n">
+        <v>385.04</v>
+      </c>
+      <c r="AB229" t="n">
+        <v>377.32</v>
+      </c>
+      <c r="AC229" t="n">
+        <v>369.59</v>
+      </c>
+      <c r="AD229" t="n">
+        <v>361.84</v>
+      </c>
+      <c r="AE229" t="n">
+        <v>360.03</v>
+      </c>
+      <c r="AF229" t="n">
+        <v>336.49</v>
+      </c>
+      <c r="AG229" t="n">
+        <v>331.45</v>
+      </c>
+      <c r="AH229" t="n">
+        <v>330.68</v>
+      </c>
+      <c r="AI229" t="n">
+        <v>315.14</v>
+      </c>
+      <c r="AJ229" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -26410,7 +26524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B229"/>
+  <dimension ref="A1:B230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28703,6 +28817,16 @@
       </c>
       <c r="B229" t="n">
         <v>0.62</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>0.87</v>
       </c>
     </row>
   </sheetData>
@@ -28871,28 +28995,28 @@
         <v>0.0307</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2419788141046113</v>
+        <v>-0.2459324541592503</v>
       </c>
       <c r="J2" t="n">
+        <v>228</v>
+      </c>
+      <c r="K2" t="n">
         <v>227</v>
       </c>
-      <c r="K2" t="n">
-        <v>226</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.02950033220405268</v>
+        <v>0.03071160310300658</v>
       </c>
       <c r="M2" t="n">
-        <v>8.164460018155504</v>
+        <v>8.151878336861815</v>
       </c>
       <c r="N2" t="n">
-        <v>128.6230721082566</v>
+        <v>128.1619560847814</v>
       </c>
       <c r="O2" t="n">
-        <v>11.34121122756545</v>
+        <v>11.32086375171</v>
       </c>
       <c r="P2" t="n">
-        <v>375.837013240507</v>
+        <v>375.8717481069398</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28949,28 +29073,28 @@
         <v>0.0407</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3838996914555645</v>
+        <v>-0.3895057029820514</v>
       </c>
       <c r="J3" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K3" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1244715947558163</v>
+        <v>0.1284288783812138</v>
       </c>
       <c r="M3" t="n">
-        <v>6.372884711462365</v>
+        <v>6.374062246890435</v>
       </c>
       <c r="N3" t="n">
-        <v>69.35771138101897</v>
+        <v>69.26591672853598</v>
       </c>
       <c r="O3" t="n">
-        <v>8.328127723625459</v>
+        <v>8.322614777132003</v>
       </c>
       <c r="P3" t="n">
-        <v>356.848259186536</v>
+        <v>356.8973144201609</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29027,28 +29151,28 @@
         <v>0.0421</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3169322468048976</v>
+        <v>-0.3200272190086771</v>
       </c>
       <c r="J4" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K4" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1061636976171818</v>
+        <v>0.1088687933554051</v>
       </c>
       <c r="M4" t="n">
-        <v>6.067003850660877</v>
+        <v>6.057151814103237</v>
       </c>
       <c r="N4" t="n">
-        <v>56.58144740698751</v>
+        <v>56.39802305712708</v>
       </c>
       <c r="O4" t="n">
-        <v>7.522064039011335</v>
+        <v>7.509861720240066</v>
       </c>
       <c r="P4" t="n">
-        <v>349.8123312665841</v>
+        <v>349.8394137268683</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29105,28 +29229,28 @@
         <v>0.0379</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2389335544741008</v>
+        <v>-0.2375686711314538</v>
       </c>
       <c r="J5" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K5" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06956598035704065</v>
+        <v>0.0694495383241327</v>
       </c>
       <c r="M5" t="n">
-        <v>5.741322247286091</v>
+        <v>5.722541565629213</v>
       </c>
       <c r="N5" t="n">
-        <v>51.08603544275972</v>
+        <v>50.87456457404453</v>
       </c>
       <c r="O5" t="n">
-        <v>7.147449576090741</v>
+        <v>7.132640785434559</v>
       </c>
       <c r="P5" t="n">
-        <v>352.7841796121837</v>
+        <v>352.7722362419413</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29183,28 +29307,28 @@
         <v>0.0309</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3033486751561238</v>
+        <v>-0.2995019563338141</v>
       </c>
       <c r="J6" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K6" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08329426961015207</v>
+        <v>0.08199780257626099</v>
       </c>
       <c r="M6" t="n">
-        <v>6.530510069071235</v>
+        <v>6.520789733122769</v>
       </c>
       <c r="N6" t="n">
-        <v>67.7576395339716</v>
+        <v>67.56046596723574</v>
       </c>
       <c r="O6" t="n">
-        <v>8.231502872135295</v>
+        <v>8.21951738043273</v>
       </c>
       <c r="P6" t="n">
-        <v>360.1567169469363</v>
+        <v>360.1230563506949</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29261,28 +29385,28 @@
         <v>0.0305</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1631582449067747</v>
+        <v>-0.1562388625028546</v>
       </c>
       <c r="J7" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K7" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01498882973899229</v>
+        <v>0.01385871782120052</v>
       </c>
       <c r="M7" t="n">
-        <v>8.683447950464785</v>
+        <v>8.681746700350899</v>
       </c>
       <c r="N7" t="n">
-        <v>117.0444217098093</v>
+        <v>116.8546575271426</v>
       </c>
       <c r="O7" t="n">
-        <v>10.81870702578683</v>
+        <v>10.80993328042049</v>
       </c>
       <c r="P7" t="n">
-        <v>370.3330255721532</v>
+        <v>370.2724777265485</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29339,28 +29463,28 @@
         <v>0.0362</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1877099442741701</v>
+        <v>-0.181310962812491</v>
       </c>
       <c r="J8" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K8" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02889152520157123</v>
+        <v>0.02717635011717601</v>
       </c>
       <c r="M8" t="n">
-        <v>7.262837067907745</v>
+        <v>7.272168597011565</v>
       </c>
       <c r="N8" t="n">
-        <v>79.23755710534266</v>
+        <v>79.16676921073987</v>
       </c>
       <c r="O8" t="n">
-        <v>8.901548017358703</v>
+        <v>8.897570972503669</v>
       </c>
       <c r="P8" t="n">
-        <v>366.9526766243317</v>
+        <v>366.8966825313689</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29417,28 +29541,28 @@
         <v>0.0308</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4316303217461778</v>
+        <v>-0.4236894505228077</v>
       </c>
       <c r="J9" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K9" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08392892758589987</v>
+        <v>0.08162293538195631</v>
       </c>
       <c r="M9" t="n">
-        <v>9.373133801322917</v>
+        <v>9.376812009980066</v>
       </c>
       <c r="N9" t="n">
-        <v>136.050652343418</v>
+        <v>135.8801206376081</v>
       </c>
       <c r="O9" t="n">
-        <v>11.66407528882671</v>
+        <v>11.65676287129528</v>
       </c>
       <c r="P9" t="n">
-        <v>367.0677141351028</v>
+        <v>366.998227782603</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29495,28 +29619,28 @@
         <v>0.0363</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5608736194260644</v>
+        <v>-0.5524315094840887</v>
       </c>
       <c r="J10" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K10" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1553756045625464</v>
+        <v>0.1521684432942604</v>
       </c>
       <c r="M10" t="n">
-        <v>8.938964003973989</v>
+        <v>8.946465120052038</v>
       </c>
       <c r="N10" t="n">
-        <v>114.4115996725622</v>
+        <v>114.3914764800161</v>
       </c>
       <c r="O10" t="n">
-        <v>10.69633580589924</v>
+        <v>10.69539510630702</v>
       </c>
       <c r="P10" t="n">
-        <v>375.8446234552468</v>
+        <v>375.7707510285609</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29573,28 +29697,28 @@
         <v>0.0417</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.649739681596524</v>
+        <v>-0.644256802004888</v>
       </c>
       <c r="J11" t="n">
+        <v>228</v>
+      </c>
+      <c r="K11" t="n">
         <v>227</v>
       </c>
-      <c r="K11" t="n">
-        <v>226</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.1896124392192213</v>
+        <v>0.1882730074417218</v>
       </c>
       <c r="M11" t="n">
-        <v>8.918710894020579</v>
+        <v>8.908502776085193</v>
       </c>
       <c r="N11" t="n">
-        <v>121.2426498171087</v>
+        <v>120.9127315795946</v>
       </c>
       <c r="O11" t="n">
-        <v>11.01102401310199</v>
+        <v>10.99603253812913</v>
       </c>
       <c r="P11" t="n">
-        <v>380.6075870740978</v>
+        <v>380.5597263850632</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -29651,28 +29775,28 @@
         <v>0.035</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7111219482916334</v>
+        <v>-0.7056224235502664</v>
       </c>
       <c r="J12" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K12" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1892909506780898</v>
+        <v>0.188206505840151</v>
       </c>
       <c r="M12" t="n">
-        <v>9.579538639066909</v>
+        <v>9.565697083078156</v>
       </c>
       <c r="N12" t="n">
-        <v>145.4540944739117</v>
+        <v>145.01646412369</v>
       </c>
       <c r="O12" t="n">
-        <v>12.06043508642668</v>
+        <v>12.04227819491354</v>
       </c>
       <c r="P12" t="n">
-        <v>382.9980783795509</v>
+        <v>382.9499006422445</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -29729,28 +29853,28 @@
         <v>0.0377</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.9313239656004585</v>
+        <v>-0.9282206128991086</v>
       </c>
       <c r="J13" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K13" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2722851080234678</v>
+        <v>0.2728298094575009</v>
       </c>
       <c r="M13" t="n">
-        <v>10.19732732647805</v>
+        <v>10.16837179546095</v>
       </c>
       <c r="N13" t="n">
-        <v>156.0908158782347</v>
+        <v>155.462967741375</v>
       </c>
       <c r="O13" t="n">
-        <v>12.49363101256935</v>
+        <v>12.46847896663322</v>
       </c>
       <c r="P13" t="n">
-        <v>389.5460296224916</v>
+        <v>389.5188474847085</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -29807,28 +29931,28 @@
         <v>0.0472</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8843801190250092</v>
+        <v>-0.8793101716676982</v>
       </c>
       <c r="J14" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K14" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3225833689809493</v>
+        <v>0.3218740676904711</v>
       </c>
       <c r="M14" t="n">
-        <v>8.425434240925924</v>
+        <v>8.413079127817438</v>
       </c>
       <c r="N14" t="n">
-        <v>110.5936632140741</v>
+        <v>110.2779914911789</v>
       </c>
       <c r="O14" t="n">
-        <v>10.51635218191527</v>
+        <v>10.50133284355747</v>
       </c>
       <c r="P14" t="n">
-        <v>393.6044462051819</v>
+        <v>393.5600387462555</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -29885,28 +30009,28 @@
         <v>0.0445</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.030006981712206</v>
+        <v>-1.023003280422271</v>
       </c>
       <c r="J15" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K15" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3781428513550005</v>
+        <v>0.3765884666465067</v>
       </c>
       <c r="M15" t="n">
-        <v>8.675874004903314</v>
+        <v>8.676898724540697</v>
       </c>
       <c r="N15" t="n">
-        <v>116.6328308059092</v>
+        <v>116.4393412878329</v>
       </c>
       <c r="O15" t="n">
-        <v>10.7996680877659</v>
+        <v>10.79070624601712</v>
       </c>
       <c r="P15" t="n">
-        <v>398.8720325143843</v>
+        <v>398.810016363243</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -29963,28 +30087,28 @@
         <v>0.0452</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9362969077893059</v>
+        <v>-0.9313252699613539</v>
       </c>
       <c r="J16" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K16" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3422013359740046</v>
+        <v>0.3416942304363653</v>
       </c>
       <c r="M16" t="n">
-        <v>8.622429338318007</v>
+        <v>8.612499674524862</v>
       </c>
       <c r="N16" t="n">
-        <v>112.6533750569677</v>
+        <v>112.3131633253746</v>
       </c>
       <c r="O16" t="n">
-        <v>10.61382942471602</v>
+        <v>10.59779049261565</v>
       </c>
       <c r="P16" t="n">
-        <v>401.8052763967564</v>
+        <v>401.7612536964448</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -30041,28 +30165,28 @@
         <v>0.0472</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9252599384291673</v>
+        <v>-0.92380084152164</v>
       </c>
       <c r="J17" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K17" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3585318710452486</v>
+        <v>0.3600411617849859</v>
       </c>
       <c r="M17" t="n">
-        <v>8.158601898912522</v>
+        <v>8.130644452598835</v>
       </c>
       <c r="N17" t="n">
-        <v>102.7280115748581</v>
+        <v>102.2839000724312</v>
       </c>
       <c r="O17" t="n">
-        <v>10.13548279929763</v>
+        <v>10.1135503198645</v>
       </c>
       <c r="P17" t="n">
-        <v>404.5266954943623</v>
+        <v>404.5138460958263</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -30119,28 +30243,28 @@
         <v>0.0468</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.01987827856637</v>
+        <v>-1.01919661860125</v>
       </c>
       <c r="J18" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K18" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3852118343105725</v>
+        <v>0.3872241430585155</v>
       </c>
       <c r="M18" t="n">
-        <v>8.542628104327912</v>
+        <v>8.508463092402733</v>
       </c>
       <c r="N18" t="n">
-        <v>111.3362555975087</v>
+        <v>110.8423825220278</v>
       </c>
       <c r="O18" t="n">
-        <v>10.55159967007414</v>
+        <v>10.52817090106481</v>
       </c>
       <c r="P18" t="n">
-        <v>407.2829960489999</v>
+        <v>407.2769930751656</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -30197,28 +30321,28 @@
         <v>0.0452</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.065127674843112</v>
+        <v>-1.062079740503756</v>
       </c>
       <c r="J19" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K19" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4120763890953419</v>
+        <v>0.4129434329151781</v>
       </c>
       <c r="M19" t="n">
-        <v>8.581819180601071</v>
+        <v>8.560321810891704</v>
       </c>
       <c r="N19" t="n">
-        <v>107.8402936961002</v>
+        <v>107.4257255611267</v>
       </c>
       <c r="O19" t="n">
-        <v>10.38461812952697</v>
+        <v>10.36463822625405</v>
       </c>
       <c r="P19" t="n">
-        <v>408.2683590841943</v>
+        <v>408.2414694774025</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -30275,28 +30399,28 @@
         <v>0.0417</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9793070236727595</v>
+        <v>-0.9727687976429276</v>
       </c>
       <c r="J20" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K20" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3108115417889303</v>
+        <v>0.3096281306817709</v>
       </c>
       <c r="M20" t="n">
-        <v>9.807397790207007</v>
+        <v>9.796418889265377</v>
       </c>
       <c r="N20" t="n">
-        <v>142.2780282289125</v>
+        <v>141.942922272837</v>
       </c>
       <c r="O20" t="n">
-        <v>11.92803538848341</v>
+        <v>11.91398011887031</v>
       </c>
       <c r="P20" t="n">
-        <v>406.5661363745964</v>
+        <v>406.5089238262685</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -30353,28 +30477,28 @@
         <v>0.0364</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.349183565086036</v>
+        <v>-1.343163969282277</v>
       </c>
       <c r="J21" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K21" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4908835459751011</v>
+        <v>0.4906375969950709</v>
       </c>
       <c r="M21" t="n">
-        <v>9.230046203577004</v>
+        <v>9.226768095997059</v>
       </c>
       <c r="N21" t="n">
-        <v>126.3106539564891</v>
+        <v>126.0015623125375</v>
       </c>
       <c r="O21" t="n">
-        <v>11.23880126866247</v>
+        <v>11.22504175103761</v>
       </c>
       <c r="P21" t="n">
-        <v>415.1421758108444</v>
+        <v>415.0895015205606</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -30431,28 +30555,28 @@
         <v>0.041</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.403230439782291</v>
+        <v>-1.401488312204815</v>
       </c>
       <c r="J22" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K22" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5783432044451867</v>
+        <v>0.5800993894782311</v>
       </c>
       <c r="M22" t="n">
-        <v>8.114962099350651</v>
+        <v>8.090442228256597</v>
       </c>
       <c r="N22" t="n">
-        <v>96.04852555605429</v>
+        <v>95.64777258314905</v>
       </c>
       <c r="O22" t="n">
-        <v>9.800434967696805</v>
+        <v>9.779967923421275</v>
       </c>
       <c r="P22" t="n">
-        <v>418.7325145110109</v>
+        <v>418.7172700765473</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -30509,28 +30633,28 @@
         <v>0.0413</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.169210094651611</v>
+        <v>-1.166841056079198</v>
       </c>
       <c r="J23" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K23" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5234564652018572</v>
+        <v>0.5248010132973071</v>
       </c>
       <c r="M23" t="n">
-        <v>7.511625708729269</v>
+        <v>7.492992145226413</v>
       </c>
       <c r="N23" t="n">
-        <v>83.26574410948695</v>
+        <v>82.93847521491197</v>
       </c>
       <c r="O23" t="n">
-        <v>9.125006526544896</v>
+        <v>9.107056341920368</v>
       </c>
       <c r="P23" t="n">
-        <v>417.2766101252432</v>
+        <v>417.2558799251557</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -30587,28 +30711,28 @@
         <v>0.0373</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.175879483608329</v>
+        <v>-1.167799403493097</v>
       </c>
       <c r="J24" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K24" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4746132798689997</v>
+        <v>0.4725679234821746</v>
       </c>
       <c r="M24" t="n">
-        <v>8.261687007816455</v>
+        <v>8.266652785563723</v>
       </c>
       <c r="N24" t="n">
-        <v>102.4056863247017</v>
+        <v>102.3977937469984</v>
       </c>
       <c r="O24" t="n">
-        <v>10.11956947328797</v>
+        <v>10.11917949969257</v>
       </c>
       <c r="P24" t="n">
-        <v>419.1130519145306</v>
+        <v>419.0423474188499</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -30665,28 +30789,28 @@
         <v>0.0417</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.425798002504492</v>
+        <v>-1.41081190233108</v>
       </c>
       <c r="J25" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K25" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L25" t="n">
-        <v>0.5885625461288887</v>
+        <v>0.5819761213428487</v>
       </c>
       <c r="M25" t="n">
-        <v>7.821047300750982</v>
+        <v>7.873486094287552</v>
       </c>
       <c r="N25" t="n">
-        <v>95.079403186088</v>
+        <v>96.18026230556485</v>
       </c>
       <c r="O25" t="n">
-        <v>9.750866791526176</v>
+        <v>9.80715362914056</v>
       </c>
       <c r="P25" t="n">
-        <v>417.0504723930123</v>
+        <v>416.9193369785274</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -30743,28 +30867,28 @@
         <v>0.0425</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.459982771132087</v>
+        <v>-1.441838943194364</v>
       </c>
       <c r="J26" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K26" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L26" t="n">
-        <v>0.5489225035979566</v>
+        <v>0.5404917910770022</v>
       </c>
       <c r="M26" t="n">
-        <v>8.770539981478802</v>
+        <v>8.842087957246539</v>
       </c>
       <c r="N26" t="n">
-        <v>117.1911534114351</v>
+        <v>118.9020869091332</v>
       </c>
       <c r="O26" t="n">
-        <v>10.82548628983636</v>
+        <v>10.9042233519464</v>
       </c>
       <c r="P26" t="n">
-        <v>407.6264554565062</v>
+        <v>407.4676884411103</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -30821,28 +30945,28 @@
         <v>0.0428</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.140791708216316</v>
+        <v>-1.123593260222658</v>
       </c>
       <c r="J27" t="n">
+        <v>228</v>
+      </c>
+      <c r="K27" t="n">
         <v>227</v>
       </c>
-      <c r="K27" t="n">
-        <v>226</v>
-      </c>
       <c r="L27" t="n">
-        <v>0.4572287561614815</v>
+        <v>0.4473767652907075</v>
       </c>
       <c r="M27" t="n">
-        <v>8.140501189572278</v>
+        <v>8.200380639599956</v>
       </c>
       <c r="N27" t="n">
-        <v>103.6868627082791</v>
+        <v>105.2392434759288</v>
       </c>
       <c r="O27" t="n">
-        <v>10.18267463431289</v>
+        <v>10.25861801004057</v>
       </c>
       <c r="P27" t="n">
-        <v>393.7644934235408</v>
+        <v>393.6141082954572</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -30899,28 +31023,28 @@
         <v>0.0419</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.048997989777639</v>
+        <v>-1.034220992035886</v>
       </c>
       <c r="J28" t="n">
+        <v>228</v>
+      </c>
+      <c r="K28" t="n">
         <v>227</v>
       </c>
-      <c r="K28" t="n">
-        <v>226</v>
-      </c>
       <c r="L28" t="n">
-        <v>0.4278112065512913</v>
+        <v>0.4196417334493179</v>
       </c>
       <c r="M28" t="n">
-        <v>7.844443018495022</v>
+        <v>7.898024574525169</v>
       </c>
       <c r="N28" t="n">
-        <v>98.77891032547804</v>
+        <v>99.82698409265301</v>
       </c>
       <c r="O28" t="n">
-        <v>9.938757987066495</v>
+        <v>9.991345459579156</v>
       </c>
       <c r="P28" t="n">
-        <v>386.640124031278</v>
+        <v>386.5109123315419</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -30977,28 +31101,28 @@
         <v>0.0419</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.9999199721748318</v>
+        <v>-0.9866506886812754</v>
       </c>
       <c r="J29" t="n">
+        <v>228</v>
+      </c>
+      <c r="K29" t="n">
         <v>227</v>
       </c>
-      <c r="K29" t="n">
-        <v>226</v>
-      </c>
       <c r="L29" t="n">
-        <v>0.3676222035066221</v>
+        <v>0.3613253227007054</v>
       </c>
       <c r="M29" t="n">
-        <v>8.157014283377228</v>
+        <v>8.198593484627207</v>
       </c>
       <c r="N29" t="n">
-        <v>115.4338267322583</v>
+        <v>116.121301744693</v>
       </c>
       <c r="O29" t="n">
-        <v>10.74401352997372</v>
+        <v>10.77595943499664</v>
       </c>
       <c r="P29" t="n">
-        <v>379.4970601306958</v>
+        <v>379.3810320508078</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -31055,28 +31179,28 @@
         <v>0.0426</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.8374213323236682</v>
+        <v>-0.8293493917415428</v>
       </c>
       <c r="J30" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K30" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L30" t="n">
-        <v>0.2841648996837463</v>
+        <v>0.2814870442087842</v>
       </c>
       <c r="M30" t="n">
-        <v>8.16176755942038</v>
+        <v>8.171243794216151</v>
       </c>
       <c r="N30" t="n">
-        <v>118.1924780346797</v>
+        <v>118.1144565864077</v>
       </c>
       <c r="O30" t="n">
-        <v>10.87163640096006</v>
+        <v>10.86804750571176</v>
       </c>
       <c r="P30" t="n">
-        <v>373.9376099918913</v>
+        <v>373.8669767209479</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -31133,28 +31257,28 @@
         <v>0.0438</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8441031454747303</v>
+        <v>-0.8384168904927157</v>
       </c>
       <c r="J31" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K31" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L31" t="n">
-        <v>0.3064634978578257</v>
+        <v>0.3052549452859448</v>
       </c>
       <c r="M31" t="n">
-        <v>8.110080436056034</v>
+        <v>8.107054262735915</v>
       </c>
       <c r="N31" t="n">
-        <v>108.2889701240132</v>
+        <v>108.0300117736174</v>
       </c>
       <c r="O31" t="n">
-        <v>10.40619863946548</v>
+        <v>10.39374868724549</v>
       </c>
       <c r="P31" t="n">
-        <v>375.2957447539004</v>
+        <v>375.2459311951541</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -31211,28 +31335,28 @@
         <v>0.0533</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.6893750251097155</v>
+        <v>-0.687101607370434</v>
       </c>
       <c r="J32" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K32" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L32" t="n">
-        <v>0.3278236352729524</v>
+        <v>0.3284186603714651</v>
       </c>
       <c r="M32" t="n">
-        <v>6.304609110105472</v>
+        <v>6.288342628064872</v>
       </c>
       <c r="N32" t="n">
-        <v>65.6133915491112</v>
+        <v>65.35713612595572</v>
       </c>
       <c r="O32" t="n">
-        <v>8.100209352177954</v>
+        <v>8.084376050503572</v>
       </c>
       <c r="P32" t="n">
-        <v>351.9232241319363</v>
+        <v>351.9033113601134</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -31289,28 +31413,28 @@
         <v>0.0528</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.5173684085783701</v>
+        <v>-0.5109384298495552</v>
       </c>
       <c r="J33" t="n">
+        <v>228</v>
+      </c>
+      <c r="K33" t="n">
         <v>227</v>
       </c>
-      <c r="K33" t="n">
-        <v>226</v>
-      </c>
       <c r="L33" t="n">
-        <v>0.2046827750522155</v>
+        <v>0.2015814032006716</v>
       </c>
       <c r="M33" t="n">
-        <v>6.372841228161033</v>
+        <v>6.383869605725574</v>
       </c>
       <c r="N33" t="n">
-        <v>69.76818672319516</v>
+        <v>69.74154569434805</v>
       </c>
       <c r="O33" t="n">
-        <v>8.352735283917189</v>
+        <v>8.351140382866765</v>
       </c>
       <c r="P33" t="n">
-        <v>337.1196983551562</v>
+        <v>337.063442221681</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -31367,28 +31491,28 @@
         <v>0.0456</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.5890288451823376</v>
+        <v>-0.5769413649324426</v>
       </c>
       <c r="J34" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K34" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L34" t="n">
-        <v>0.1432967728840469</v>
+        <v>0.1386077394956363</v>
       </c>
       <c r="M34" t="n">
-        <v>8.836870106463925</v>
+        <v>8.880329330410067</v>
       </c>
       <c r="N34" t="n">
-        <v>139.7568881476679</v>
+        <v>140.1353785738448</v>
       </c>
       <c r="O34" t="n">
-        <v>11.82188175155157</v>
+        <v>11.83787897276555</v>
       </c>
       <c r="P34" t="n">
-        <v>331.1730069090494</v>
+        <v>331.0675194923824</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -31445,28 +31569,28 @@
         <v>0.0526</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1467755397888527</v>
+        <v>-0.13622834034035</v>
       </c>
       <c r="J35" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K35" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L35" t="n">
-        <v>0.005599707266067955</v>
+        <v>0.004860860401823652</v>
       </c>
       <c r="M35" t="n">
-        <v>12.98401524480503</v>
+        <v>12.97928885960193</v>
       </c>
       <c r="N35" t="n">
-        <v>258.6200556467491</v>
+        <v>258.2335922184847</v>
       </c>
       <c r="O35" t="n">
-        <v>16.08166831043188</v>
+        <v>16.0696481672277</v>
       </c>
       <c r="P35" t="n">
-        <v>305.8316547926465</v>
+        <v>305.739696714191</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
@@ -31504,7 +31628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ228"/>
+  <dimension ref="A1:AJ229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72819,6 +72943,188 @@
         </is>
       </c>
     </row>
+    <row r="229">
+      <c r="A229" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:17:45+00:00</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>-34.506689095829415,172.70232119337555</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>-34.505917219641795,172.70236848769468</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>-34.505193984457435,172.70217558011043</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>-34.504498066655934,172.70184776061978</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>-34.50379731798731,172.70153919679123</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>-34.50314308222566,172.70112161137746</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>-34.502532230781696,172.7006465708671</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>-34.50190839117088,172.70016054569467</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>-34.50133917335539,172.699582432463</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>-34.50073176549113,172.6990686922689</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>-34.50013517339107,172.69853671168985</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>-34.499522557052096,172.69803173727607</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>-34.49896267051674,172.6974378643072</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>-34.49838155969953,172.69687976365734</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>-34.497798521960895,172.69633072100868</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>-34.497209338260355,172.6957958605263</t>
+        </is>
+      </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>-34.496629979177634,172.69523955303038</t>
+        </is>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>-34.49606880586241,172.694652814302</t>
+        </is>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>-34.49552020123475,172.69404711844376</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>-34.4949330283913,172.6934995697681</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>-34.49433846589109,172.69296315722033</t>
+        </is>
+      </c>
+      <c r="W229" t="inlineStr">
+        <is>
+          <t>-34.493793062572664,172.69235261633943</t>
+        </is>
+      </c>
+      <c r="X229" t="inlineStr">
+        <is>
+          <t>-34.4932818641862,172.69172987908675</t>
+        </is>
+      </c>
+      <c r="Y229" t="inlineStr">
+        <is>
+          <t>-34.49279211723267,172.69109971616004</t>
+        </is>
+      </c>
+      <c r="Z229" t="inlineStr">
+        <is>
+          <t>-34.492260506069236,172.69047866752086</t>
+        </is>
+      </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>-34.49172436333506,172.68985502573233</t>
+        </is>
+      </c>
+      <c r="AB229" t="inlineStr">
+        <is>
+          <t>-34.49118055323647,172.6892396586481</t>
+        </is>
+      </c>
+      <c r="AC229" t="inlineStr">
+        <is>
+          <t>-34.49063667336751,172.68862436395307</t>
+        </is>
+      </c>
+      <c r="AD229" t="inlineStr">
+        <is>
+          <t>-34.4900925969492,172.68800906518797</t>
+        </is>
+      </c>
+      <c r="AE229" t="inlineStr">
+        <is>
+          <t>-34.489592123172756,172.68733806556887</t>
+        </is>
+      </c>
+      <c r="AF229" t="inlineStr">
+        <is>
+          <t>-34.48911370055862,172.68659643125568</t>
+        </is>
+      </c>
+      <c r="AG229" t="inlineStr">
+        <is>
+          <t>-34.488791691357726,172.68578569905696</t>
+        </is>
+      </c>
+      <c r="AH229" t="inlineStr">
+        <is>
+          <t>-34.48850529206676,172.68495727135445</t>
+        </is>
+      </c>
+      <c r="AI229" t="inlineStr">
+        <is>
+          <t>-34.48809571422877,172.68419005455362</t>
+        </is>
+      </c>
+      <c r="AJ229" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0008/nzd0008.xlsx
+++ b/data/nzd0008/nzd0008.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ229"/>
+  <dimension ref="A1:AJ231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26510,6 +26510,234 @@
       <c r="AJ229" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>374.33</v>
+      </c>
+      <c r="C230" t="n">
+        <v>347</v>
+      </c>
+      <c r="D230" t="n">
+        <v>345</v>
+      </c>
+      <c r="E230" t="n">
+        <v>353.66</v>
+      </c>
+      <c r="F230" t="n">
+        <v>362.74</v>
+      </c>
+      <c r="G230" t="n">
+        <v>379.72</v>
+      </c>
+      <c r="H230" t="n">
+        <v>373.9</v>
+      </c>
+      <c r="I230" t="n">
+        <v>373.2</v>
+      </c>
+      <c r="J230" t="n">
+        <v>375.82</v>
+      </c>
+      <c r="K230" t="n">
+        <v>374.84</v>
+      </c>
+      <c r="L230" t="n">
+        <v>378.73</v>
+      </c>
+      <c r="M230" t="n">
+        <v>379.12</v>
+      </c>
+      <c r="N230" t="n">
+        <v>387.21</v>
+      </c>
+      <c r="O230" t="n">
+        <v>390.84</v>
+      </c>
+      <c r="P230" t="n">
+        <v>390.46</v>
+      </c>
+      <c r="Q230" t="n">
+        <v>382.91</v>
+      </c>
+      <c r="R230" t="n">
+        <v>377.75</v>
+      </c>
+      <c r="S230" t="n">
+        <v>380.01</v>
+      </c>
+      <c r="T230" t="n">
+        <v>389.57</v>
+      </c>
+      <c r="U230" t="n">
+        <v>392.23</v>
+      </c>
+      <c r="V230" t="n">
+        <v>391.28</v>
+      </c>
+      <c r="W230" t="n">
+        <v>396.34</v>
+      </c>
+      <c r="X230" t="n">
+        <v>405.73</v>
+      </c>
+      <c r="Y230" t="n">
+        <v>402.19</v>
+      </c>
+      <c r="Z230" t="n">
+        <v>395.44</v>
+      </c>
+      <c r="AA230" t="n">
+        <v>388.75</v>
+      </c>
+      <c r="AB230" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="AC230" t="n">
+        <v>371.7</v>
+      </c>
+      <c r="AD230" t="n">
+        <v>363.52</v>
+      </c>
+      <c r="AE230" t="n">
+        <v>361.62</v>
+      </c>
+      <c r="AF230" t="n">
+        <v>339.19</v>
+      </c>
+      <c r="AG230" t="n">
+        <v>332.88</v>
+      </c>
+      <c r="AH230" t="n">
+        <v>332.67</v>
+      </c>
+      <c r="AI230" t="n">
+        <v>318.13</v>
+      </c>
+      <c r="AJ230" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>376.44</v>
+      </c>
+      <c r="C231" t="n">
+        <v>347.58</v>
+      </c>
+      <c r="D231" t="n">
+        <v>346.36</v>
+      </c>
+      <c r="E231" t="n">
+        <v>354.71</v>
+      </c>
+      <c r="F231" t="n">
+        <v>364.62</v>
+      </c>
+      <c r="G231" t="n">
+        <v>381.36</v>
+      </c>
+      <c r="H231" t="n">
+        <v>375.73</v>
+      </c>
+      <c r="I231" t="n">
+        <v>374.58</v>
+      </c>
+      <c r="J231" t="n">
+        <v>376.79</v>
+      </c>
+      <c r="K231" t="n">
+        <v>376.03</v>
+      </c>
+      <c r="L231" t="n">
+        <v>380.07</v>
+      </c>
+      <c r="M231" t="n">
+        <v>381.57</v>
+      </c>
+      <c r="N231" t="n">
+        <v>389.15</v>
+      </c>
+      <c r="O231" t="n">
+        <v>392.65</v>
+      </c>
+      <c r="P231" t="n">
+        <v>392.18</v>
+      </c>
+      <c r="Q231" t="n">
+        <v>385.01</v>
+      </c>
+      <c r="R231" t="n">
+        <v>378.5</v>
+      </c>
+      <c r="S231" t="n">
+        <v>379.62</v>
+      </c>
+      <c r="T231" t="n">
+        <v>388.65</v>
+      </c>
+      <c r="U231" t="n">
+        <v>393.23</v>
+      </c>
+      <c r="V231" t="n">
+        <v>395.03</v>
+      </c>
+      <c r="W231" t="n">
+        <v>400.21</v>
+      </c>
+      <c r="X231" t="n">
+        <v>408.88</v>
+      </c>
+      <c r="Y231" t="n">
+        <v>404.92</v>
+      </c>
+      <c r="Z231" t="n">
+        <v>397.41</v>
+      </c>
+      <c r="AA231" t="n">
+        <v>389.28</v>
+      </c>
+      <c r="AB231" t="n">
+        <v>380.73</v>
+      </c>
+      <c r="AC231" t="n">
+        <v>373.14</v>
+      </c>
+      <c r="AD231" t="n">
+        <v>366.21</v>
+      </c>
+      <c r="AE231" t="n">
+        <v>365.29</v>
+      </c>
+      <c r="AF231" t="n">
+        <v>342.56</v>
+      </c>
+      <c r="AG231" t="n">
+        <v>335.96</v>
+      </c>
+      <c r="AH231" t="n">
+        <v>335.23</v>
+      </c>
+      <c r="AI231" t="n">
+        <v>319.58</v>
+      </c>
+      <c r="AJ231" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -26524,7 +26752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B230"/>
+  <dimension ref="A1:B232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28827,6 +29055,26 @@
       </c>
       <c r="B230" t="n">
         <v>0.87</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
@@ -28995,28 +29243,28 @@
         <v>0.0307</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2459324541592503</v>
+        <v>-0.236272860387694</v>
       </c>
       <c r="J2" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K2" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03071160310300658</v>
+        <v>0.02889780452110668</v>
       </c>
       <c r="M2" t="n">
-        <v>8.151878336861815</v>
+        <v>8.128400964173972</v>
       </c>
       <c r="N2" t="n">
-        <v>128.1619560847814</v>
+        <v>127.3667750621067</v>
       </c>
       <c r="O2" t="n">
-        <v>11.32086375171</v>
+        <v>11.28568894937773</v>
       </c>
       <c r="P2" t="n">
-        <v>375.8717481069398</v>
+        <v>375.7859331260918</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29073,28 +29321,28 @@
         <v>0.0407</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3895057029820514</v>
+        <v>-0.3882346532334915</v>
       </c>
       <c r="J3" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K3" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1284288783812138</v>
+        <v>0.1299280785799296</v>
       </c>
       <c r="M3" t="n">
-        <v>6.374062246890435</v>
+        <v>6.325794888252509</v>
       </c>
       <c r="N3" t="n">
-        <v>69.26591672853598</v>
+        <v>68.66981507075924</v>
       </c>
       <c r="O3" t="n">
-        <v>8.322614777132003</v>
+        <v>8.28672523200566</v>
       </c>
       <c r="P3" t="n">
-        <v>356.8973144201609</v>
+        <v>356.8860653229331</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29151,28 +29399,28 @@
         <v>0.0421</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3200272190086771</v>
+        <v>-0.3130763843577509</v>
       </c>
       <c r="J4" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K4" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1088687933554051</v>
+        <v>0.1062818729920445</v>
       </c>
       <c r="M4" t="n">
-        <v>6.057151814103237</v>
+        <v>6.042389913957687</v>
       </c>
       <c r="N4" t="n">
-        <v>56.39802305712708</v>
+        <v>56.07472241920667</v>
       </c>
       <c r="O4" t="n">
-        <v>7.509861720240066</v>
+        <v>7.488305710853869</v>
       </c>
       <c r="P4" t="n">
-        <v>349.8394137268683</v>
+        <v>349.7779115130581</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29229,28 +29477,28 @@
         <v>0.0379</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2375686711314538</v>
+        <v>-0.2252909449762181</v>
       </c>
       <c r="J5" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K5" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0694495383241327</v>
+        <v>0.06348074817821592</v>
       </c>
       <c r="M5" t="n">
-        <v>5.722541565629213</v>
+        <v>5.729263783844107</v>
       </c>
       <c r="N5" t="n">
-        <v>50.87456457404453</v>
+        <v>50.94332554259235</v>
       </c>
       <c r="O5" t="n">
-        <v>7.132640785434559</v>
+        <v>7.137459319855515</v>
       </c>
       <c r="P5" t="n">
-        <v>352.7722362419413</v>
+        <v>352.6636113109901</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29307,28 +29555,28 @@
         <v>0.0309</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2995019563338141</v>
+        <v>-0.2812077126746852</v>
       </c>
       <c r="J6" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K6" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08199780257626099</v>
+        <v>0.0732066946411426</v>
       </c>
       <c r="M6" t="n">
-        <v>6.520789733122769</v>
+        <v>6.556784973065625</v>
       </c>
       <c r="N6" t="n">
-        <v>67.56046596723574</v>
+        <v>68.11012717351699</v>
       </c>
       <c r="O6" t="n">
-        <v>8.21951738043273</v>
+        <v>8.252885990580324</v>
       </c>
       <c r="P6" t="n">
-        <v>360.1230563506949</v>
+        <v>359.9611989950126</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29385,28 +29633,28 @@
         <v>0.0305</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1562388625028546</v>
+        <v>-0.1333905921086513</v>
       </c>
       <c r="J7" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K7" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01385871782120052</v>
+        <v>0.01018820932901743</v>
       </c>
       <c r="M7" t="n">
-        <v>8.681746700350899</v>
+        <v>8.723767122699313</v>
       </c>
       <c r="N7" t="n">
-        <v>116.8546575271426</v>
+        <v>117.6062249835204</v>
       </c>
       <c r="O7" t="n">
-        <v>10.80993328042049</v>
+        <v>10.84464038055299</v>
       </c>
       <c r="P7" t="n">
-        <v>370.2724777265485</v>
+        <v>370.0703343423863</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29463,28 +29711,28 @@
         <v>0.0362</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.181310962812491</v>
+        <v>-0.1611179558163312</v>
       </c>
       <c r="J8" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K8" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02717635011717601</v>
+        <v>0.02163588644461123</v>
       </c>
       <c r="M8" t="n">
-        <v>7.272168597011565</v>
+        <v>7.335729979151861</v>
       </c>
       <c r="N8" t="n">
-        <v>79.16676921073987</v>
+        <v>79.86175560414908</v>
       </c>
       <c r="O8" t="n">
-        <v>8.897570972503669</v>
+        <v>8.936540471801662</v>
       </c>
       <c r="P8" t="n">
-        <v>366.8966825313689</v>
+        <v>366.7180278555283</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29541,28 +29789,28 @@
         <v>0.0308</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4236894505228077</v>
+        <v>-0.3948679165946437</v>
       </c>
       <c r="J9" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K9" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08162293538195631</v>
+        <v>0.07161961979808529</v>
       </c>
       <c r="M9" t="n">
-        <v>9.376812009980066</v>
+        <v>9.455856604970629</v>
       </c>
       <c r="N9" t="n">
-        <v>135.8801206376081</v>
+        <v>137.5063597679517</v>
       </c>
       <c r="O9" t="n">
-        <v>11.65676287129528</v>
+        <v>11.72631057783955</v>
       </c>
       <c r="P9" t="n">
-        <v>366.998227782603</v>
+        <v>366.7432429451925</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29619,28 +29867,28 @@
         <v>0.0363</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5524315094840887</v>
+        <v>-0.5282289379407703</v>
       </c>
       <c r="J10" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K10" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1521684432942604</v>
+        <v>0.1412870673836709</v>
       </c>
       <c r="M10" t="n">
-        <v>8.946465120052038</v>
+        <v>8.999276946576273</v>
       </c>
       <c r="N10" t="n">
-        <v>114.3914764800161</v>
+        <v>115.3759041829991</v>
       </c>
       <c r="O10" t="n">
-        <v>10.69539510630702</v>
+        <v>10.74131761856985</v>
       </c>
       <c r="P10" t="n">
-        <v>375.7707510285609</v>
+        <v>375.5566316803693</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29697,28 +29945,28 @@
         <v>0.0417</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.644256802004888</v>
+        <v>-0.6251312036261114</v>
       </c>
       <c r="J11" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K11" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1882730074417218</v>
+        <v>0.180653614043348</v>
       </c>
       <c r="M11" t="n">
-        <v>8.908502776085193</v>
+        <v>8.93178095423885</v>
       </c>
       <c r="N11" t="n">
-        <v>120.9127315795946</v>
+        <v>121.100569736965</v>
       </c>
       <c r="O11" t="n">
-        <v>10.99603253812913</v>
+        <v>11.00457040219949</v>
       </c>
       <c r="P11" t="n">
-        <v>380.5597263850632</v>
+        <v>380.3909185912797</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -29775,28 +30023,28 @@
         <v>0.035</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7056224235502664</v>
+        <v>-0.6813824385650938</v>
       </c>
       <c r="J12" t="n">
+        <v>230</v>
+      </c>
+      <c r="K12" t="n">
         <v>228</v>
       </c>
-      <c r="K12" t="n">
-        <v>226</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.188206505840151</v>
+        <v>0.1786428446490872</v>
       </c>
       <c r="M12" t="n">
-        <v>9.565697083078156</v>
+        <v>9.605154097722947</v>
       </c>
       <c r="N12" t="n">
-        <v>145.01646412369</v>
+        <v>145.7461942307229</v>
       </c>
       <c r="O12" t="n">
-        <v>12.04227819491354</v>
+        <v>12.07253884776201</v>
       </c>
       <c r="P12" t="n">
-        <v>382.9499006422445</v>
+        <v>382.7351782419645</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -29853,28 +30101,28 @@
         <v>0.0377</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.9282206128991086</v>
+        <v>-0.9034784104728677</v>
       </c>
       <c r="J13" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K13" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2728298094575009</v>
+        <v>0.2634588211416712</v>
       </c>
       <c r="M13" t="n">
-        <v>10.16837179546095</v>
+        <v>10.20591684175387</v>
       </c>
       <c r="N13" t="n">
-        <v>155.462967741375</v>
+        <v>156.1973218551475</v>
       </c>
       <c r="O13" t="n">
-        <v>12.46847896663322</v>
+        <v>12.49789269657679</v>
       </c>
       <c r="P13" t="n">
-        <v>389.5188474847085</v>
+        <v>389.2996865219404</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -29931,28 +30179,28 @@
         <v>0.0472</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8793101716676982</v>
+        <v>-0.8506225698668125</v>
       </c>
       <c r="J14" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K14" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3218740676904711</v>
+        <v>0.3063724319758161</v>
       </c>
       <c r="M14" t="n">
-        <v>8.413079127817438</v>
+        <v>8.484221612296697</v>
       </c>
       <c r="N14" t="n">
-        <v>110.2779914911789</v>
+        <v>112.1254507634033</v>
       </c>
       <c r="O14" t="n">
-        <v>10.50133284355747</v>
+        <v>10.58893057694701</v>
       </c>
       <c r="P14" t="n">
-        <v>393.5600387462555</v>
+        <v>393.3059374784012</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -30009,28 +30257,28 @@
         <v>0.0445</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.023003280422271</v>
+        <v>-0.990513568260279</v>
       </c>
       <c r="J15" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K15" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3765884666465067</v>
+        <v>0.3591232458863497</v>
       </c>
       <c r="M15" t="n">
-        <v>8.676898724540697</v>
+        <v>8.780926644965268</v>
       </c>
       <c r="N15" t="n">
-        <v>116.4393412878329</v>
+        <v>118.972112716889</v>
       </c>
       <c r="O15" t="n">
-        <v>10.79070624601712</v>
+        <v>10.907433828215</v>
       </c>
       <c r="P15" t="n">
-        <v>398.810016363243</v>
+        <v>398.5190971885655</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -30087,28 +30335,28 @@
         <v>0.0452</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9313252699613539</v>
+        <v>-0.9081759866888013</v>
       </c>
       <c r="J16" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K16" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3416942304363653</v>
+        <v>0.3312885591638238</v>
       </c>
       <c r="M16" t="n">
-        <v>8.612499674524862</v>
+        <v>8.666832094519529</v>
       </c>
       <c r="N16" t="n">
-        <v>112.3131633253746</v>
+        <v>113.1268407290251</v>
       </c>
       <c r="O16" t="n">
-        <v>10.59779049261565</v>
+        <v>10.63611022550186</v>
       </c>
       <c r="P16" t="n">
-        <v>401.7612536964448</v>
+        <v>401.5539670752075</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -30165,28 +30413,28 @@
         <v>0.0472</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.92380084152164</v>
+        <v>-0.917226694336558</v>
       </c>
       <c r="J17" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K17" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3600411617849859</v>
+        <v>0.3609697402805783</v>
       </c>
       <c r="M17" t="n">
-        <v>8.130644452598835</v>
+        <v>8.096238201031081</v>
       </c>
       <c r="N17" t="n">
-        <v>102.2839000724312</v>
+        <v>101.5356363508085</v>
       </c>
       <c r="O17" t="n">
-        <v>10.1135503198645</v>
+        <v>10.07648928698922</v>
       </c>
       <c r="P17" t="n">
-        <v>404.5138460958263</v>
+        <v>404.4552877633456</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -30243,28 +30491,28 @@
         <v>0.0468</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.01919661860125</v>
+        <v>-1.022248132611996</v>
       </c>
       <c r="J18" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K18" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3872241430585155</v>
+        <v>0.393300601128456</v>
       </c>
       <c r="M18" t="n">
-        <v>8.508463092402733</v>
+        <v>8.448835184352887</v>
       </c>
       <c r="N18" t="n">
-        <v>110.8423825220278</v>
+        <v>109.8945369141052</v>
       </c>
       <c r="O18" t="n">
-        <v>10.52817090106481</v>
+        <v>10.48305952067931</v>
       </c>
       <c r="P18" t="n">
-        <v>407.2769930751656</v>
+        <v>407.3041599084455</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -30321,28 +30569,28 @@
         <v>0.0452</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.062079740503756</v>
+        <v>-1.062152930197174</v>
       </c>
       <c r="J19" t="n">
+        <v>230</v>
+      </c>
+      <c r="K19" t="n">
         <v>228</v>
       </c>
-      <c r="K19" t="n">
-        <v>226</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.4129434329151781</v>
+        <v>0.4178166365141086</v>
       </c>
       <c r="M19" t="n">
-        <v>8.560321810891704</v>
+        <v>8.486704668809752</v>
       </c>
       <c r="N19" t="n">
-        <v>107.4257255611267</v>
+        <v>106.4836577577501</v>
       </c>
       <c r="O19" t="n">
-        <v>10.36463822625405</v>
+        <v>10.31909190567417</v>
       </c>
       <c r="P19" t="n">
-        <v>408.2414694774025</v>
+        <v>408.242124899013</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -30399,28 +30647,28 @@
         <v>0.0417</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9727687976429276</v>
+        <v>-0.959171241109627</v>
       </c>
       <c r="J20" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K20" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3096281306817709</v>
+        <v>0.3069333729016153</v>
       </c>
       <c r="M20" t="n">
-        <v>9.796418889265377</v>
+        <v>9.776068040401773</v>
       </c>
       <c r="N20" t="n">
-        <v>141.942922272837</v>
+        <v>141.3345428571663</v>
       </c>
       <c r="O20" t="n">
-        <v>11.91398011887031</v>
+        <v>11.88842053668889</v>
       </c>
       <c r="P20" t="n">
-        <v>406.5089238262685</v>
+        <v>406.3886377534581</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -30477,28 +30725,28 @@
         <v>0.0364</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.343163969282277</v>
+        <v>-1.321751339948852</v>
       </c>
       <c r="J21" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K21" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4906375969950709</v>
+        <v>0.4845120308878258</v>
       </c>
       <c r="M21" t="n">
-        <v>9.226768095997059</v>
+        <v>9.276612301453065</v>
       </c>
       <c r="N21" t="n">
-        <v>126.0015623125375</v>
+        <v>126.4557649027648</v>
       </c>
       <c r="O21" t="n">
-        <v>11.22504175103761</v>
+        <v>11.24525521732454</v>
       </c>
       <c r="P21" t="n">
-        <v>415.0895015205606</v>
+        <v>414.9000633101247</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -30555,28 +30803,28 @@
         <v>0.041</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.401488312204815</v>
+        <v>-1.382676749064571</v>
       </c>
       <c r="J22" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K22" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5800993894782311</v>
+        <v>0.5752410832310404</v>
       </c>
       <c r="M22" t="n">
-        <v>8.090442228256597</v>
+        <v>8.13668891645756</v>
       </c>
       <c r="N22" t="n">
-        <v>95.64777258314905</v>
+        <v>96.04153103499908</v>
       </c>
       <c r="O22" t="n">
-        <v>9.779967923421275</v>
+        <v>9.800078113719252</v>
       </c>
       <c r="P22" t="n">
-        <v>418.7172700765473</v>
+        <v>418.5508213592084</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -30633,28 +30881,28 @@
         <v>0.0413</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.166841056079198</v>
+        <v>-1.147530520941182</v>
       </c>
       <c r="J23" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K23" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5248010132973071</v>
+        <v>0.5175628054233217</v>
       </c>
       <c r="M23" t="n">
-        <v>7.492992145226413</v>
+        <v>7.541414696548481</v>
       </c>
       <c r="N23" t="n">
-        <v>82.93847521491197</v>
+        <v>83.50863049850749</v>
       </c>
       <c r="O23" t="n">
-        <v>9.107056341920368</v>
+        <v>9.138305668914095</v>
       </c>
       <c r="P23" t="n">
-        <v>417.2558799251557</v>
+        <v>417.0850161936535</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -30711,28 +30959,28 @@
         <v>0.0373</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.167799403493097</v>
+        <v>-1.136993578296228</v>
       </c>
       <c r="J24" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K24" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4725679234821746</v>
+        <v>0.4564544200769538</v>
       </c>
       <c r="M24" t="n">
-        <v>8.266652785563723</v>
+        <v>8.352966025033787</v>
       </c>
       <c r="N24" t="n">
-        <v>102.3977937469984</v>
+        <v>104.7320781113993</v>
       </c>
       <c r="O24" t="n">
-        <v>10.11917949969257</v>
+        <v>10.23386916622444</v>
       </c>
       <c r="P24" t="n">
-        <v>419.0423474188499</v>
+        <v>418.7697943489884</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -30789,28 +31037,28 @@
         <v>0.0417</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.41081190233108</v>
+        <v>-1.372304931063637</v>
       </c>
       <c r="J25" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K25" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L25" t="n">
-        <v>0.5819761213428487</v>
+        <v>0.5607426200696124</v>
       </c>
       <c r="M25" t="n">
-        <v>7.873486094287552</v>
+        <v>8.029893859232988</v>
       </c>
       <c r="N25" t="n">
-        <v>96.18026230556485</v>
+        <v>100.364908688723</v>
       </c>
       <c r="O25" t="n">
-        <v>9.80715362914056</v>
+        <v>10.01822881994233</v>
       </c>
       <c r="P25" t="n">
-        <v>416.9193369785274</v>
+        <v>416.5786577421059</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -30867,28 +31115,28 @@
         <v>0.0425</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.441838943194364</v>
+        <v>-1.398356727253008</v>
       </c>
       <c r="J26" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K26" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L26" t="n">
-        <v>0.5404917910770022</v>
+        <v>0.517053046121327</v>
       </c>
       <c r="M26" t="n">
-        <v>8.842087957246539</v>
+        <v>9.033604724926633</v>
       </c>
       <c r="N26" t="n">
-        <v>118.9020869091332</v>
+        <v>124.2583058450264</v>
       </c>
       <c r="O26" t="n">
-        <v>10.9042233519464</v>
+        <v>11.14712096664544</v>
       </c>
       <c r="P26" t="n">
-        <v>407.4676884411103</v>
+        <v>407.0830007749485</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -30945,28 +31193,28 @@
         <v>0.0428</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.123593260222658</v>
+        <v>-1.083376631518821</v>
       </c>
       <c r="J27" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K27" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L27" t="n">
-        <v>0.4473767652907075</v>
+        <v>0.4217690983932986</v>
       </c>
       <c r="M27" t="n">
-        <v>8.200380639599956</v>
+        <v>8.361427905114125</v>
       </c>
       <c r="N27" t="n">
-        <v>105.2392434759288</v>
+        <v>109.8069455613486</v>
       </c>
       <c r="O27" t="n">
-        <v>10.25861801004057</v>
+        <v>10.47888093077446</v>
       </c>
       <c r="P27" t="n">
-        <v>393.6141082954572</v>
+        <v>393.2585527875427</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -31023,28 +31271,28 @@
         <v>0.0419</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.034220992035886</v>
+        <v>-1.000236795134846</v>
       </c>
       <c r="J28" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K28" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L28" t="n">
-        <v>0.4196417334493179</v>
+        <v>0.3989152364092883</v>
       </c>
       <c r="M28" t="n">
-        <v>7.898024574525169</v>
+        <v>8.036229986557478</v>
       </c>
       <c r="N28" t="n">
-        <v>99.82698409265301</v>
+        <v>102.8738734499388</v>
       </c>
       <c r="O28" t="n">
-        <v>9.991345459579156</v>
+        <v>10.14267585255187</v>
       </c>
       <c r="P28" t="n">
-        <v>386.5109123315419</v>
+        <v>386.2104554328018</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -31101,28 +31349,28 @@
         <v>0.0419</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.9866506886812754</v>
+        <v>-0.9559569947711908</v>
       </c>
       <c r="J29" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K29" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3613253227007054</v>
+        <v>0.3451728062793729</v>
       </c>
       <c r="M29" t="n">
-        <v>8.198593484627207</v>
+        <v>8.30212453319391</v>
       </c>
       <c r="N29" t="n">
-        <v>116.121301744693</v>
+        <v>118.3072031763229</v>
       </c>
       <c r="O29" t="n">
-        <v>10.77595943499664</v>
+        <v>10.87691147230329</v>
       </c>
       <c r="P29" t="n">
-        <v>379.3810320508078</v>
+        <v>379.1096608065205</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -31179,28 +31427,28 @@
         <v>0.0426</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.8293493917415428</v>
+        <v>-0.808517980408791</v>
       </c>
       <c r="J30" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K30" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L30" t="n">
-        <v>0.2814870442087842</v>
+        <v>0.2727759445499414</v>
       </c>
       <c r="M30" t="n">
-        <v>8.171243794216151</v>
+        <v>8.215105032457553</v>
       </c>
       <c r="N30" t="n">
-        <v>118.1144565864077</v>
+        <v>118.5677773622282</v>
       </c>
       <c r="O30" t="n">
-        <v>10.86804750571176</v>
+        <v>10.8888832008718</v>
       </c>
       <c r="P30" t="n">
-        <v>373.8669767209479</v>
+        <v>373.6826674928266</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -31257,28 +31505,28 @@
         <v>0.0438</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8384168904927157</v>
+        <v>-0.8216076428667384</v>
       </c>
       <c r="J31" t="n">
+        <v>230</v>
+      </c>
+      <c r="K31" t="n">
         <v>228</v>
       </c>
-      <c r="K31" t="n">
-        <v>226</v>
-      </c>
       <c r="L31" t="n">
-        <v>0.3052549452859448</v>
+        <v>0.2989655463420099</v>
       </c>
       <c r="M31" t="n">
-        <v>8.107054262735915</v>
+        <v>8.132675202515985</v>
       </c>
       <c r="N31" t="n">
-        <v>108.0300117736174</v>
+        <v>108.0727228553055</v>
       </c>
       <c r="O31" t="n">
-        <v>10.39374868724549</v>
+        <v>10.39580313661746</v>
       </c>
       <c r="P31" t="n">
-        <v>375.2459311951541</v>
+        <v>375.0970101792602</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -31335,28 +31583,28 @@
         <v>0.0533</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.687101607370434</v>
+        <v>-0.6754896435412134</v>
       </c>
       <c r="J32" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K32" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L32" t="n">
-        <v>0.3284186603714651</v>
+        <v>0.3236472932136301</v>
       </c>
       <c r="M32" t="n">
-        <v>6.288342628064872</v>
+        <v>6.291424647019469</v>
       </c>
       <c r="N32" t="n">
-        <v>65.35713612595572</v>
+        <v>65.26680897296797</v>
       </c>
       <c r="O32" t="n">
-        <v>8.084376050503572</v>
+        <v>8.07878759300973</v>
       </c>
       <c r="P32" t="n">
-        <v>351.9033113601134</v>
+        <v>351.8004377194152</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -31413,28 +31661,28 @@
         <v>0.0528</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.5109384298495552</v>
+        <v>-0.4935113610180825</v>
       </c>
       <c r="J33" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K33" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2015814032006716</v>
+        <v>0.1913896198808112</v>
       </c>
       <c r="M33" t="n">
-        <v>6.383869605725574</v>
+        <v>6.432273586630445</v>
       </c>
       <c r="N33" t="n">
-        <v>69.74154569434805</v>
+        <v>70.18261939281663</v>
       </c>
       <c r="O33" t="n">
-        <v>8.351140382866765</v>
+        <v>8.377506752776545</v>
       </c>
       <c r="P33" t="n">
-        <v>337.063442221681</v>
+        <v>336.9092613011287</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -31491,28 +31739,28 @@
         <v>0.0456</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.5769413649324426</v>
+        <v>-0.547994235592934</v>
       </c>
       <c r="J34" t="n">
+        <v>230</v>
+      </c>
+      <c r="K34" t="n">
         <v>228</v>
       </c>
-      <c r="K34" t="n">
-        <v>226</v>
-      </c>
       <c r="L34" t="n">
-        <v>0.1386077394956363</v>
+        <v>0.1267072110729415</v>
       </c>
       <c r="M34" t="n">
-        <v>8.880329330410067</v>
+        <v>8.997863890946938</v>
       </c>
       <c r="N34" t="n">
-        <v>140.1353785738448</v>
+        <v>141.7750029536988</v>
       </c>
       <c r="O34" t="n">
-        <v>11.83787897276555</v>
+        <v>11.90693087884946</v>
       </c>
       <c r="P34" t="n">
-        <v>331.0675194923824</v>
+        <v>330.8120620332101</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -31569,28 +31817,28 @@
         <v>0.0526</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.13622834034035</v>
+        <v>-0.1097331592105514</v>
       </c>
       <c r="J35" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K35" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L35" t="n">
-        <v>0.004860860401823652</v>
+        <v>0.003192586750647597</v>
       </c>
       <c r="M35" t="n">
-        <v>12.97928885960193</v>
+        <v>12.99425745055968</v>
       </c>
       <c r="N35" t="n">
-        <v>258.2335922184847</v>
+        <v>258.3668149340944</v>
       </c>
       <c r="O35" t="n">
-        <v>16.0696481672277</v>
+        <v>16.07379279865503</v>
       </c>
       <c r="P35" t="n">
-        <v>305.739696714191</v>
+        <v>305.5060875969295</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
@@ -31628,7 +31876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ229"/>
+  <dimension ref="A1:AJ231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73125,6 +73373,370 @@
         </is>
       </c>
     </row>
+    <row r="230">
+      <c r="A230" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>-34.50671016182912,172.70221717650503</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>-34.50593292815403,172.7022909255023</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>-34.5052099714935,172.70209664298756</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>-34.50450985323248,172.7017895634619</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>-34.503810416901786,172.7014779167357</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>-34.50316268309389,172.70107183605126</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>-34.50255282072705,172.70061186054403</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>-34.50194852038288,172.70009289633094</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>-34.50136165400306,172.69954453481407</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>-34.50075587430286,172.69902804989837</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>-34.500175669694435,172.6984684434418</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>-34.49957707712355,172.6979398279483</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>-34.49901892357201,172.6973430333694</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>-34.498437339758866,172.69678573002795</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>-34.49783791936905,172.69626660945673</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>-34.497215406561956,172.69578652032322</t>
+        </is>
+      </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>-34.496611091582494,172.69526803169907</t>
+        </is>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>-34.49604726846653,172.69468528836467</t>
+        </is>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>-34.49552459890011,172.69404048763462</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>-34.49496302259086,172.6934543444303</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>-34.49438108904888,172.69289888991344</t>
+        </is>
+      </c>
+      <c r="W230" t="inlineStr">
+        <is>
+          <t>-34.493833035679245,172.69229234468824</t>
+        </is>
+      </c>
+      <c r="X230" t="inlineStr">
+        <is>
+          <t>-34.493328715855284,172.69166827361195</t>
+        </is>
+      </c>
+      <c r="Y230" t="inlineStr">
+        <is>
+          <t>-34.492819899890584,172.69106878456947</t>
+        </is>
+      </c>
+      <c r="Z230" t="inlineStr">
+        <is>
+          <t>-34.492286189966926,172.69045093933678</t>
+        </is>
+      </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>-34.491749307560774,172.6898280960632</t>
+        </is>
+      </c>
+      <c r="AB230" t="inlineStr">
+        <is>
+          <t>-34.4911985049527,172.68922027804444</t>
+        </is>
+      </c>
+      <c r="AC230" t="inlineStr">
+        <is>
+          <t>-34.490650859883694,172.68860904823228</t>
+        </is>
+      </c>
+      <c r="AD230" t="inlineStr">
+        <is>
+          <t>-34.49010394647156,172.6879969442459</t>
+        </is>
+      </c>
+      <c r="AE230" t="inlineStr">
+        <is>
+          <t>-34.48960431427765,172.68732894921143</t>
+        </is>
+      </c>
+      <c r="AF230" t="inlineStr">
+        <is>
+          <t>-34.48913621793864,172.68658524201547</t>
+        </is>
+      </c>
+      <c r="AG230" t="inlineStr">
+        <is>
+          <t>-34.488803617204546,172.68577977285435</t>
+        </is>
+      </c>
+      <c r="AH230" t="inlineStr">
+        <is>
+          <t>-34.488521888139104,172.68494902432377</t>
+        </is>
+      </c>
+      <c r="AI230" t="inlineStr">
+        <is>
+          <t>-34.48812064998839,172.68417766320627</t>
+        </is>
+      </c>
+      <c r="AJ230" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>-34.50671468361401,172.70219484937752</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>-34.50593417111741,172.70228478824708</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>-34.50521288601466,172.70208225230243</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>-34.50451210339393,172.70177845309354</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>-34.50381465544238,172.7014580877292</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>-34.50316903594008,172.70105570333186</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>-34.502562432866455,172.7005956564843</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>-34.50195576884906,172.70008067693635</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>-34.50136674891454,172.6995359458581</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>-34.5007621247333,172.6990175129837</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>-34.50018270795851,172.69845657839588</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>-34.499589945530936,172.6979181344961</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>-34.499029113193075,172.69732585576298</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>-34.49844684652248,172.6967697035683</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>-34.49784716404921,172.69625156553678</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>-34.49722709778315,172.69576852543278</t>
+        </is>
+      </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>-34.496615320149154,172.69526165587882</t>
+        </is>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>-34.496045069621964,172.6946886037785</t>
+        </is>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>-34.495519411910166,172.69404830858892</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>-34.494968660596385,172.69344584342335</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>-34.49440223147547,172.69286701126475</t>
+        </is>
+      </c>
+      <c r="W231" t="inlineStr">
+        <is>
+          <t>-34.49385485455539,172.69225944603352</t>
+        </is>
+      </c>
+      <c r="X231" t="inlineStr">
+        <is>
+          <t>-34.49334793235099,172.6916430057215</t>
+        </is>
+      </c>
+      <c r="Y231" t="inlineStr">
+        <is>
+          <t>-34.49283800171346,172.69104863104002</t>
+        </is>
+      </c>
+      <c r="Z231" t="inlineStr">
+        <is>
+          <t>-34.49229943532524,172.69043663971692</t>
+        </is>
+      </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>-34.4917528710211,172.6898242489663</t>
+        </is>
+      </c>
+      <c r="AB231" t="inlineStr">
+        <is>
+          <t>-34.49120348033418,172.68921490663973</t>
+        </is>
+      </c>
+      <c r="AC231" t="inlineStr">
+        <is>
+          <t>-34.490660541675595,172.68859859579428</t>
+        </is>
+      </c>
+      <c r="AD231" t="inlineStr">
+        <is>
+          <t>-34.490122119216075,172.68797753630201</t>
+        </is>
+      </c>
+      <c r="AE231" t="inlineStr">
+        <is>
+          <t>-34.48963245349185,172.68730790704294</t>
+        </is>
+      </c>
+      <c r="AF231" t="inlineStr">
+        <is>
+          <t>-34.489164322963234,172.6865712761775</t>
+        </is>
+      </c>
+      <c r="AG231" t="inlineStr">
+        <is>
+          <t>-34.488829303642746,172.68576700871986</t>
+        </is>
+      </c>
+      <c r="AH231" t="inlineStr">
+        <is>
+          <t>-34.488543237859375,172.68493841507345</t>
+        </is>
+      </c>
+      <c r="AI231" t="inlineStr">
+        <is>
+          <t>-34.488132742580355,172.68417165402178</t>
+        </is>
+      </c>
+      <c r="AJ231" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0008/nzd0008.xlsx
+++ b/data/nzd0008/nzd0008.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ231"/>
+  <dimension ref="A1:AJ232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26738,6 +26738,120 @@
       <c r="AJ231" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>378.05</v>
+      </c>
+      <c r="C232" t="n">
+        <v>348.82</v>
+      </c>
+      <c r="D232" t="n">
+        <v>346.19</v>
+      </c>
+      <c r="E232" t="n">
+        <v>354.97</v>
+      </c>
+      <c r="F232" t="n">
+        <v>366.34</v>
+      </c>
+      <c r="G232" t="n">
+        <v>380.81</v>
+      </c>
+      <c r="H232" t="n">
+        <v>373.94</v>
+      </c>
+      <c r="I232" t="n">
+        <v>370.83</v>
+      </c>
+      <c r="J232" t="n">
+        <v>372.86</v>
+      </c>
+      <c r="K232" t="n">
+        <v>374.81</v>
+      </c>
+      <c r="L232" t="n">
+        <v>378.82</v>
+      </c>
+      <c r="M232" t="n">
+        <v>385.52</v>
+      </c>
+      <c r="N232" t="n">
+        <v>394.58</v>
+      </c>
+      <c r="O232" t="n">
+        <v>397.05</v>
+      </c>
+      <c r="P232" t="n">
+        <v>394.26</v>
+      </c>
+      <c r="Q232" t="n">
+        <v>384.13</v>
+      </c>
+      <c r="R232" t="n">
+        <v>375.43</v>
+      </c>
+      <c r="S232" t="n">
+        <v>375.82</v>
+      </c>
+      <c r="T232" t="n">
+        <v>384.79</v>
+      </c>
+      <c r="U232" t="n">
+        <v>391.19</v>
+      </c>
+      <c r="V232" t="n">
+        <v>395.65</v>
+      </c>
+      <c r="W232" t="n">
+        <v>403.01</v>
+      </c>
+      <c r="X232" t="n">
+        <v>411.1</v>
+      </c>
+      <c r="Y232" t="n">
+        <v>406.92</v>
+      </c>
+      <c r="Z232" t="n">
+        <v>397.8</v>
+      </c>
+      <c r="AA232" t="n">
+        <v>388.07</v>
+      </c>
+      <c r="AB232" t="n">
+        <v>380.05</v>
+      </c>
+      <c r="AC232" t="n">
+        <v>372.48</v>
+      </c>
+      <c r="AD232" t="n">
+        <v>367.26</v>
+      </c>
+      <c r="AE232" t="n">
+        <v>366.38</v>
+      </c>
+      <c r="AF232" t="n">
+        <v>345</v>
+      </c>
+      <c r="AG232" t="n">
+        <v>336</v>
+      </c>
+      <c r="AH232" t="n">
+        <v>335.01</v>
+      </c>
+      <c r="AI232" t="n">
+        <v>322.21</v>
+      </c>
+      <c r="AJ232" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -26752,7 +26866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B232"/>
+  <dimension ref="A1:B233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29075,6 +29189,16 @@
       </c>
       <c r="B232" t="n">
         <v>0.4</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>-0.64</v>
       </c>
     </row>
   </sheetData>
@@ -29243,28 +29367,28 @@
         <v>0.0307</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.236272860387694</v>
+        <v>-0.229498190495374</v>
       </c>
       <c r="J2" t="n">
+        <v>231</v>
+      </c>
+      <c r="K2" t="n">
         <v>230</v>
       </c>
-      <c r="K2" t="n">
-        <v>229</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.02889780452110668</v>
+        <v>0.02750457397851624</v>
       </c>
       <c r="M2" t="n">
-        <v>8.128400964173972</v>
+        <v>8.126164775913743</v>
       </c>
       <c r="N2" t="n">
-        <v>127.3667750621067</v>
+        <v>127.1300389955729</v>
       </c>
       <c r="O2" t="n">
-        <v>11.28568894937773</v>
+        <v>11.27519574089838</v>
       </c>
       <c r="P2" t="n">
-        <v>375.7859331260918</v>
+        <v>375.7254961222638</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29321,28 +29445,28 @@
         <v>0.0407</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3882346532334915</v>
+        <v>-0.3863949816748242</v>
       </c>
       <c r="J3" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K3" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1299280785799296</v>
+        <v>0.129927874185385</v>
       </c>
       <c r="M3" t="n">
-        <v>6.325794888252509</v>
+        <v>6.308670785701186</v>
       </c>
       <c r="N3" t="n">
-        <v>68.66981507075924</v>
+        <v>68.39595590950128</v>
       </c>
       <c r="O3" t="n">
-        <v>8.28672523200566</v>
+        <v>8.270184756672688</v>
       </c>
       <c r="P3" t="n">
-        <v>356.8860653229331</v>
+        <v>356.8697193315757</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29399,28 +29523,28 @@
         <v>0.0421</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3130763843577509</v>
+        <v>-0.3092993010466726</v>
       </c>
       <c r="J4" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K4" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1062818729920445</v>
+        <v>0.1047527465351393</v>
       </c>
       <c r="M4" t="n">
-        <v>6.042389913957687</v>
+        <v>6.03695340637098</v>
       </c>
       <c r="N4" t="n">
-        <v>56.07472241920667</v>
+        <v>55.93066745400019</v>
       </c>
       <c r="O4" t="n">
-        <v>7.488305710853869</v>
+        <v>7.478680863227163</v>
       </c>
       <c r="P4" t="n">
-        <v>349.7779115130581</v>
+        <v>349.7443510816494</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29477,28 +29601,28 @@
         <v>0.0379</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2252909449762181</v>
+        <v>-0.2187365550307726</v>
       </c>
       <c r="J5" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K5" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06348074817821592</v>
+        <v>0.06028550396093579</v>
       </c>
       <c r="M5" t="n">
-        <v>5.729263783844107</v>
+        <v>5.734787891995847</v>
       </c>
       <c r="N5" t="n">
-        <v>50.94332554259235</v>
+        <v>51.01998336652423</v>
       </c>
       <c r="O5" t="n">
-        <v>7.137459319855515</v>
+        <v>7.142827407023372</v>
       </c>
       <c r="P5" t="n">
-        <v>352.6636113109901</v>
+        <v>352.6053737408668</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29555,28 +29679,28 @@
         <v>0.0309</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2812077126746852</v>
+        <v>-0.2702784010669754</v>
       </c>
       <c r="J6" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K6" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0732066946411426</v>
+        <v>0.06786247861705252</v>
       </c>
       <c r="M6" t="n">
-        <v>6.556784973065625</v>
+        <v>6.585030421822619</v>
       </c>
       <c r="N6" t="n">
-        <v>68.11012717351699</v>
+        <v>68.64161617264327</v>
       </c>
       <c r="O6" t="n">
-        <v>8.252885990580324</v>
+        <v>8.285023607247192</v>
       </c>
       <c r="P6" t="n">
-        <v>359.9611989950126</v>
+        <v>359.8640890341388</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29633,28 +29757,28 @@
         <v>0.0305</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1333905921086513</v>
+        <v>-0.1221460217645674</v>
       </c>
       <c r="J7" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K7" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01018820932901743</v>
+        <v>0.00857736334906245</v>
       </c>
       <c r="M7" t="n">
-        <v>8.723767122699313</v>
+        <v>8.744589825804752</v>
       </c>
       <c r="N7" t="n">
-        <v>117.6062249835204</v>
+        <v>117.9718045702852</v>
       </c>
       <c r="O7" t="n">
-        <v>10.84464038055299</v>
+        <v>10.86148261381867</v>
       </c>
       <c r="P7" t="n">
-        <v>370.0703343423863</v>
+        <v>369.9704232203183</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29711,28 +29835,28 @@
         <v>0.0362</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1611179558163312</v>
+        <v>-0.1520551696174502</v>
       </c>
       <c r="J8" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K8" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02163588644461123</v>
+        <v>0.0193676163105263</v>
       </c>
       <c r="M8" t="n">
-        <v>7.335729979151861</v>
+        <v>7.360712781251255</v>
       </c>
       <c r="N8" t="n">
-        <v>79.86175560414908</v>
+        <v>80.08422634722912</v>
       </c>
       <c r="O8" t="n">
-        <v>8.936540471801662</v>
+        <v>8.948979067314278</v>
       </c>
       <c r="P8" t="n">
-        <v>366.7180278555283</v>
+        <v>366.6375024899087</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29789,28 +29913,28 @@
         <v>0.0308</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3948679165946437</v>
+        <v>-0.3833415884444763</v>
       </c>
       <c r="J9" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K9" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L9" t="n">
-        <v>0.07161961979808529</v>
+        <v>0.06797798443444525</v>
       </c>
       <c r="M9" t="n">
-        <v>9.455856604970629</v>
+        <v>9.478429078101522</v>
       </c>
       <c r="N9" t="n">
-        <v>137.5063597679517</v>
+        <v>137.8301757701665</v>
       </c>
       <c r="O9" t="n">
-        <v>11.72631057783955</v>
+        <v>11.74010970009082</v>
       </c>
       <c r="P9" t="n">
-        <v>366.7432429451925</v>
+        <v>366.6408283269752</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29867,28 +29991,28 @@
         <v>0.0363</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5282289379407703</v>
+        <v>-0.5192277163044549</v>
       </c>
       <c r="J10" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K10" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1412870673836709</v>
+        <v>0.1377574027915395</v>
       </c>
       <c r="M10" t="n">
-        <v>8.999276946576273</v>
+        <v>9.008369618097218</v>
       </c>
       <c r="N10" t="n">
-        <v>115.3759041829991</v>
+        <v>115.4369406457462</v>
       </c>
       <c r="O10" t="n">
-        <v>10.74131761856985</v>
+        <v>10.7441584428817</v>
       </c>
       <c r="P10" t="n">
-        <v>375.5566316803693</v>
+        <v>375.4766533329404</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29945,28 +30069,28 @@
         <v>0.0417</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6251312036261114</v>
+        <v>-0.6163499410306068</v>
       </c>
       <c r="J11" t="n">
+        <v>231</v>
+      </c>
+      <c r="K11" t="n">
         <v>230</v>
       </c>
-      <c r="K11" t="n">
-        <v>229</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.180653614043348</v>
+        <v>0.1772892632746986</v>
       </c>
       <c r="M11" t="n">
-        <v>8.93178095423885</v>
+        <v>8.939599462119315</v>
       </c>
       <c r="N11" t="n">
-        <v>121.100569736965</v>
+        <v>121.1101445926878</v>
       </c>
       <c r="O11" t="n">
-        <v>11.00457040219949</v>
+        <v>11.00500543356012</v>
       </c>
       <c r="P11" t="n">
-        <v>380.3909185912797</v>
+        <v>380.31307616491</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30023,28 +30147,28 @@
         <v>0.035</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6813824385650938</v>
+        <v>-0.6700973748573105</v>
       </c>
       <c r="J12" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K12" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1786428446490872</v>
+        <v>0.1743271863401945</v>
       </c>
       <c r="M12" t="n">
-        <v>9.605154097722947</v>
+        <v>9.620121170005016</v>
       </c>
       <c r="N12" t="n">
-        <v>145.7461942307229</v>
+        <v>145.9971807369759</v>
       </c>
       <c r="O12" t="n">
-        <v>12.07253884776201</v>
+        <v>12.08292931109737</v>
       </c>
       <c r="P12" t="n">
-        <v>382.7351782419645</v>
+        <v>382.6347765989393</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30101,28 +30225,28 @@
         <v>0.0377</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.9034784104728677</v>
+        <v>-0.8874136829145091</v>
       </c>
       <c r="J13" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K13" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2634588211416712</v>
+        <v>0.2562189243990025</v>
       </c>
       <c r="M13" t="n">
-        <v>10.20591684175387</v>
+        <v>10.24278387090108</v>
       </c>
       <c r="N13" t="n">
-        <v>156.1973218551475</v>
+        <v>157.3185851194502</v>
       </c>
       <c r="O13" t="n">
-        <v>12.49789269657679</v>
+        <v>12.54267057366373</v>
       </c>
       <c r="P13" t="n">
-        <v>389.2996865219404</v>
+        <v>389.156769080396</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30179,28 +30303,28 @@
         <v>0.0472</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8506225698668125</v>
+        <v>-0.831698027800312</v>
       </c>
       <c r="J14" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K14" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3063724319758161</v>
+        <v>0.2943075374448202</v>
       </c>
       <c r="M14" t="n">
-        <v>8.484221612296697</v>
+        <v>8.544841076356356</v>
       </c>
       <c r="N14" t="n">
-        <v>112.1254507634033</v>
+        <v>114.140378149302</v>
       </c>
       <c r="O14" t="n">
-        <v>10.58893057694701</v>
+        <v>10.68365003869474</v>
       </c>
       <c r="P14" t="n">
-        <v>393.3059374784012</v>
+        <v>393.1375781256069</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -30257,28 +30381,28 @@
         <v>0.0445</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.990513568260279</v>
+        <v>-0.9705568102357921</v>
       </c>
       <c r="J15" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K15" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3591232458863497</v>
+        <v>0.3468155581552903</v>
       </c>
       <c r="M15" t="n">
-        <v>8.780926644965268</v>
+        <v>8.852194284620246</v>
       </c>
       <c r="N15" t="n">
-        <v>118.972112716889</v>
+        <v>121.200175002268</v>
       </c>
       <c r="O15" t="n">
-        <v>10.907433828215</v>
+        <v>11.00909510369803</v>
       </c>
       <c r="P15" t="n">
-        <v>398.5190971885655</v>
+        <v>398.3396166399273</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -30335,28 +30459,28 @@
         <v>0.0452</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9081759866888013</v>
+        <v>-0.8946096853282773</v>
       </c>
       <c r="J16" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K16" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3312885591638238</v>
+        <v>0.3243414303259933</v>
       </c>
       <c r="M16" t="n">
-        <v>8.666832094519529</v>
+        <v>8.704376153751719</v>
       </c>
       <c r="N16" t="n">
-        <v>113.1268407290251</v>
+        <v>113.8980050756263</v>
       </c>
       <c r="O16" t="n">
-        <v>10.63611022550186</v>
+        <v>10.67230083326113</v>
       </c>
       <c r="P16" t="n">
-        <v>401.5539670752075</v>
+        <v>401.4319589209677</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -30413,28 +30537,28 @@
         <v>0.0472</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.917226694336558</v>
+        <v>-0.9138564791816566</v>
       </c>
       <c r="J17" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K17" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3609697402805783</v>
+        <v>0.361349901051756</v>
       </c>
       <c r="M17" t="n">
-        <v>8.096238201031081</v>
+        <v>8.079765594763808</v>
       </c>
       <c r="N17" t="n">
-        <v>101.5356363508085</v>
+        <v>101.1674570023852</v>
       </c>
       <c r="O17" t="n">
-        <v>10.07648928698922</v>
+        <v>10.05820346793528</v>
       </c>
       <c r="P17" t="n">
-        <v>404.4552877633456</v>
+        <v>404.425143574369</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -30491,28 +30615,28 @@
         <v>0.0468</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.022248132611996</v>
+        <v>-1.025776802856432</v>
       </c>
       <c r="J18" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K18" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L18" t="n">
-        <v>0.393300601128456</v>
+        <v>0.3970989713582757</v>
       </c>
       <c r="M18" t="n">
-        <v>8.448835184352887</v>
+        <v>8.429505485187248</v>
       </c>
       <c r="N18" t="n">
-        <v>109.8945369141052</v>
+        <v>109.4971484160787</v>
       </c>
       <c r="O18" t="n">
-        <v>10.48305952067931</v>
+        <v>10.46408851339087</v>
       </c>
       <c r="P18" t="n">
-        <v>407.3041599084455</v>
+        <v>407.3357213660366</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -30569,28 +30693,28 @@
         <v>0.0452</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.062152930197174</v>
+        <v>-1.065275553029081</v>
       </c>
       <c r="J19" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K19" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4178166365141086</v>
+        <v>0.4214859281181075</v>
       </c>
       <c r="M19" t="n">
-        <v>8.486704668809752</v>
+        <v>8.466929927766872</v>
       </c>
       <c r="N19" t="n">
-        <v>106.4836577577501</v>
+        <v>106.0858980360555</v>
       </c>
       <c r="O19" t="n">
-        <v>10.31909190567417</v>
+        <v>10.29980087361185</v>
       </c>
       <c r="P19" t="n">
-        <v>408.242124899013</v>
+        <v>408.2700985945334</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -30647,28 +30771,28 @@
         <v>0.0417</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.959171241109627</v>
+        <v>-0.9559410118609016</v>
       </c>
       <c r="J20" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K20" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3069333729016153</v>
+        <v>0.3074825955617518</v>
       </c>
       <c r="M20" t="n">
-        <v>9.776068040401773</v>
+        <v>9.748965914099346</v>
       </c>
       <c r="N20" t="n">
-        <v>141.3345428571663</v>
+        <v>140.7948886556264</v>
       </c>
       <c r="O20" t="n">
-        <v>11.88842053668889</v>
+        <v>11.86570219816874</v>
       </c>
       <c r="P20" t="n">
-        <v>406.3886377534581</v>
+        <v>406.3599362718629</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -30725,28 +30849,28 @@
         <v>0.0364</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.321751339948852</v>
+        <v>-1.312545787838254</v>
       </c>
       <c r="J21" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K21" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4845120308878258</v>
+        <v>0.4823186753386807</v>
       </c>
       <c r="M21" t="n">
-        <v>9.276612301453065</v>
+        <v>9.292919106328805</v>
       </c>
       <c r="N21" t="n">
-        <v>126.4557649027648</v>
+        <v>126.4945724355461</v>
       </c>
       <c r="O21" t="n">
-        <v>11.24525521732454</v>
+        <v>11.24698059194316</v>
       </c>
       <c r="P21" t="n">
-        <v>414.9000633101247</v>
+        <v>414.8182694298357</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -30803,28 +30927,28 @@
         <v>0.041</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.382676749064571</v>
+        <v>-1.371549997115103</v>
       </c>
       <c r="J22" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K22" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5752410832310404</v>
+        <v>0.5715141475027239</v>
       </c>
       <c r="M22" t="n">
-        <v>8.13668891645756</v>
+        <v>8.17101436053335</v>
       </c>
       <c r="N22" t="n">
-        <v>96.04153103499908</v>
+        <v>96.48223048804708</v>
       </c>
       <c r="O22" t="n">
-        <v>9.800078113719252</v>
+        <v>9.822536866209619</v>
       </c>
       <c r="P22" t="n">
-        <v>418.5508213592084</v>
+        <v>418.4519570862103</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -30881,28 +31005,28 @@
         <v>0.0413</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.147530520941182</v>
+        <v>-1.13441907574002</v>
       </c>
       <c r="J23" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K23" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5175628054233217</v>
+        <v>0.5107322406643493</v>
       </c>
       <c r="M23" t="n">
-        <v>7.541414696548481</v>
+        <v>7.585021641973345</v>
       </c>
       <c r="N23" t="n">
-        <v>83.50863049850749</v>
+        <v>84.33637153381645</v>
       </c>
       <c r="O23" t="n">
-        <v>9.138305668914095</v>
+        <v>9.183483627350595</v>
       </c>
       <c r="P23" t="n">
-        <v>417.0850161936535</v>
+        <v>416.9685173713868</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -30959,28 +31083,28 @@
         <v>0.0373</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.136993578296228</v>
+        <v>-1.119072912722853</v>
       </c>
       <c r="J24" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K24" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4564544200769538</v>
+        <v>0.4458037929373749</v>
       </c>
       <c r="M24" t="n">
-        <v>8.352966025033787</v>
+        <v>8.413181532733683</v>
       </c>
       <c r="N24" t="n">
-        <v>104.7320781113993</v>
+        <v>106.5003668199138</v>
       </c>
       <c r="O24" t="n">
-        <v>10.23386916622444</v>
+        <v>10.31990149274274</v>
       </c>
       <c r="P24" t="n">
-        <v>418.7697943489884</v>
+        <v>418.6105642716397</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -31037,28 +31161,28 @@
         <v>0.0417</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.372304931063637</v>
+        <v>-1.35099134777803</v>
       </c>
       <c r="J25" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K25" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L25" t="n">
-        <v>0.5607426200696124</v>
+        <v>0.547790473293317</v>
       </c>
       <c r="M25" t="n">
-        <v>8.029893859232988</v>
+        <v>8.124263124780029</v>
       </c>
       <c r="N25" t="n">
-        <v>100.364908688723</v>
+        <v>103.0729993353819</v>
       </c>
       <c r="O25" t="n">
-        <v>10.01822881994233</v>
+        <v>10.15248734721605</v>
       </c>
       <c r="P25" t="n">
-        <v>416.5786577421059</v>
+        <v>416.3892806511017</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -31115,28 +31239,28 @@
         <v>0.0425</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.398356727253008</v>
+        <v>-1.376204723403123</v>
       </c>
       <c r="J26" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K26" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L26" t="n">
-        <v>0.517053046121327</v>
+        <v>0.5047682834184066</v>
       </c>
       <c r="M26" t="n">
-        <v>9.033604724926633</v>
+        <v>9.13491588592615</v>
       </c>
       <c r="N26" t="n">
-        <v>124.2583058450264</v>
+        <v>127.1150657918271</v>
       </c>
       <c r="O26" t="n">
-        <v>11.14712096664544</v>
+        <v>11.27453173270744</v>
       </c>
       <c r="P26" t="n">
-        <v>407.0830007749485</v>
+        <v>406.886174085002</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -31193,28 +31317,28 @@
         <v>0.0428</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.083376631518821</v>
+        <v>-1.064639823843502</v>
       </c>
       <c r="J27" t="n">
+        <v>231</v>
+      </c>
+      <c r="K27" t="n">
         <v>230</v>
       </c>
-      <c r="K27" t="n">
-        <v>229</v>
-      </c>
       <c r="L27" t="n">
-        <v>0.4217690983932986</v>
+        <v>0.410315140939337</v>
       </c>
       <c r="M27" t="n">
-        <v>8.361427905114125</v>
+        <v>8.43825467428192</v>
       </c>
       <c r="N27" t="n">
-        <v>109.8069455613486</v>
+        <v>111.7700400856917</v>
       </c>
       <c r="O27" t="n">
-        <v>10.47888093077446</v>
+        <v>10.57213507696963</v>
       </c>
       <c r="P27" t="n">
-        <v>393.2585527875427</v>
+        <v>393.0921743666612</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -31271,28 +31395,28 @@
         <v>0.0419</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.000236795134846</v>
+        <v>-0.9840186746429737</v>
       </c>
       <c r="J28" t="n">
+        <v>231</v>
+      </c>
+      <c r="K28" t="n">
         <v>230</v>
       </c>
-      <c r="K28" t="n">
-        <v>229</v>
-      </c>
       <c r="L28" t="n">
-        <v>0.3989152364092883</v>
+        <v>0.3892291237717566</v>
       </c>
       <c r="M28" t="n">
-        <v>8.036229986557478</v>
+        <v>8.102336703017015</v>
       </c>
       <c r="N28" t="n">
-        <v>102.8738734499388</v>
+        <v>104.2550811999948</v>
       </c>
       <c r="O28" t="n">
-        <v>10.14267585255187</v>
+        <v>10.21053775273344</v>
       </c>
       <c r="P28" t="n">
-        <v>386.2104554328018</v>
+        <v>386.066442358437</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -31349,28 +31473,28 @@
         <v>0.0419</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.9559569947711908</v>
+        <v>-0.9410381901106079</v>
       </c>
       <c r="J29" t="n">
+        <v>231</v>
+      </c>
+      <c r="K29" t="n">
         <v>230</v>
       </c>
-      <c r="K29" t="n">
-        <v>229</v>
-      </c>
       <c r="L29" t="n">
-        <v>0.3451728062793729</v>
+        <v>0.3373753593064668</v>
       </c>
       <c r="M29" t="n">
-        <v>8.30212453319391</v>
+        <v>8.350467261798112</v>
       </c>
       <c r="N29" t="n">
-        <v>118.3072031763229</v>
+        <v>119.3400670128389</v>
       </c>
       <c r="O29" t="n">
-        <v>10.87691147230329</v>
+        <v>10.92428794076936</v>
       </c>
       <c r="P29" t="n">
-        <v>379.1096608065205</v>
+        <v>378.9771853494481</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -31427,28 +31551,28 @@
         <v>0.0426</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.808517980408791</v>
+        <v>-0.7965385928044056</v>
       </c>
       <c r="J30" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K30" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L30" t="n">
-        <v>0.2727759445499414</v>
+        <v>0.2671809875649448</v>
       </c>
       <c r="M30" t="n">
-        <v>8.215105032457553</v>
+        <v>8.245292317468502</v>
       </c>
       <c r="N30" t="n">
-        <v>118.5677773622282</v>
+        <v>119.047250288687</v>
       </c>
       <c r="O30" t="n">
-        <v>10.8888832008718</v>
+        <v>10.91087761312934</v>
       </c>
       <c r="P30" t="n">
-        <v>373.6826674928266</v>
+        <v>373.5762273158686</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -31505,28 +31629,28 @@
         <v>0.0438</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8216076428667384</v>
+        <v>-0.8111446594461436</v>
       </c>
       <c r="J31" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K31" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L31" t="n">
-        <v>0.2989655463420099</v>
+        <v>0.2941893882784719</v>
       </c>
       <c r="M31" t="n">
-        <v>8.132675202515985</v>
+        <v>8.157235085195635</v>
       </c>
       <c r="N31" t="n">
-        <v>108.0727228553055</v>
+        <v>108.3636384344555</v>
       </c>
       <c r="O31" t="n">
-        <v>10.39580313661746</v>
+        <v>10.40978570550112</v>
       </c>
       <c r="P31" t="n">
-        <v>375.0970101792602</v>
+        <v>375.0039224702693</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -31583,28 +31707,28 @@
         <v>0.0533</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.6754896435412134</v>
+        <v>-0.6666021506071198</v>
       </c>
       <c r="J32" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K32" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L32" t="n">
-        <v>0.3236472932136301</v>
+        <v>0.3181607235839641</v>
       </c>
       <c r="M32" t="n">
-        <v>6.291424647019469</v>
+        <v>6.309134040505938</v>
       </c>
       <c r="N32" t="n">
-        <v>65.26680897296797</v>
+        <v>65.53340588803442</v>
       </c>
       <c r="O32" t="n">
-        <v>8.07878759300973</v>
+        <v>8.095270587697142</v>
       </c>
       <c r="P32" t="n">
-        <v>351.8004377194152</v>
+        <v>351.721371470251</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -31661,28 +31785,28 @@
         <v>0.0528</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.4935113610180825</v>
+        <v>-0.4838336667573889</v>
       </c>
       <c r="J33" t="n">
+        <v>231</v>
+      </c>
+      <c r="K33" t="n">
         <v>230</v>
       </c>
-      <c r="K33" t="n">
-        <v>229</v>
-      </c>
       <c r="L33" t="n">
-        <v>0.1913896198808112</v>
+        <v>0.1854177587079519</v>
       </c>
       <c r="M33" t="n">
-        <v>6.432273586630445</v>
+        <v>6.462825722570956</v>
       </c>
       <c r="N33" t="n">
-        <v>70.18261939281663</v>
+        <v>70.52824780097544</v>
       </c>
       <c r="O33" t="n">
-        <v>8.377506752776545</v>
+        <v>8.39810977547778</v>
       </c>
       <c r="P33" t="n">
-        <v>336.9092613011287</v>
+        <v>336.8232778870404</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -31739,28 +31863,28 @@
         <v>0.0456</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.547994235592934</v>
+        <v>-0.5331609043805222</v>
       </c>
       <c r="J34" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K34" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L34" t="n">
-        <v>0.1267072110729415</v>
+        <v>0.1206504065612901</v>
       </c>
       <c r="M34" t="n">
-        <v>8.997863890946938</v>
+        <v>9.060501057451326</v>
       </c>
       <c r="N34" t="n">
-        <v>141.7750029536988</v>
+        <v>142.6922900325203</v>
       </c>
       <c r="O34" t="n">
-        <v>11.90693087884946</v>
+        <v>11.94538781423694</v>
       </c>
       <c r="P34" t="n">
-        <v>330.8120620332101</v>
+        <v>330.6805892134276</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -31817,28 +31941,28 @@
         <v>0.0526</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1097331592105514</v>
+        <v>-0.09431233871932615</v>
       </c>
       <c r="J35" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K35" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L35" t="n">
-        <v>0.003192586750647597</v>
+        <v>0.002368149525134311</v>
       </c>
       <c r="M35" t="n">
-        <v>12.99425745055968</v>
+        <v>13.01161007280307</v>
       </c>
       <c r="N35" t="n">
-        <v>258.3668149340944</v>
+        <v>258.9025597353099</v>
       </c>
       <c r="O35" t="n">
-        <v>16.07379279865503</v>
+        <v>16.09044933292137</v>
       </c>
       <c r="P35" t="n">
-        <v>305.5060875969295</v>
+        <v>305.3695220664934</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
@@ -31876,7 +32000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ231"/>
+  <dimension ref="A1:AJ232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73737,6 +73861,188 @@
         </is>
       </c>
     </row>
+    <row r="232">
+      <c r="A232" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>-34.50671813388314,172.70217781303694</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>-34.50593682848639,172.70227166721813</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>-34.505212521699605,172.70208405113814</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>-34.50451266057661,172.70177570195463</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>-34.50381853325328,172.70143994629598</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>-34.50316690541264,172.70106111369532</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>-34.50255303082847,172.70061150635698</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>-34.501936071927204,172.70011388180802</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>-34.501346106640526,172.6995707444052</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>-34.500755716728975,172.69902831553486</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>-34.50017614241371,172.69846764653582</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>-34.49961069254685,172.69788315932448</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>-34.49905763361422,172.69727777615168</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>-34.49846995687813,172.69673074420373</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>-34.49785834365994,172.69623337288496</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>-34.497222198605066,172.6957760661494</t>
+        </is>
+      </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>-34.49659801121415,172.69528775423228</t>
+        </is>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>-34.49602364497771,172.6947209078017</t>
+        </is>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>-34.49549764909892,172.6940811225823</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>-34.494957159064455,172.69346318547633</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>-34.49440572702252,172.69286174065994</t>
+        </is>
+      </c>
+      <c r="W232" t="inlineStr">
+        <is>
+          <t>-34.49387064081673,172.6922356433786</t>
+        </is>
+      </c>
+      <c r="X232" t="inlineStr">
+        <is>
+          <t>-34.49336147540188,172.69162519786795</t>
+        </is>
+      </c>
+      <c r="Y232" t="inlineStr">
+        <is>
+          <t>-34.49285126312,172.69103386654402</t>
+        </is>
+      </c>
+      <c r="Z232" t="inlineStr">
+        <is>
+          <t>-34.49230205750257,172.69043380882715</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>-34.491744735573775,172.68983303196063</t>
+        </is>
+      </c>
+      <c r="AB232" t="inlineStr">
+        <is>
+          <t>-34.49119890836204,172.68921984252515</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>-34.49065610418776,172.68860338649534</t>
+        </is>
+      </c>
+      <c r="AD232" t="inlineStr">
+        <is>
+          <t>-34.49012921266567,172.68796996070824</t>
+        </is>
+      </c>
+      <c r="AE232" t="inlineStr">
+        <is>
+          <t>-34.489640810914416,172.68730165745882</t>
+        </is>
+      </c>
+      <c r="AF232" t="inlineStr">
+        <is>
+          <t>-34.489184672000704,172.68656116440758</t>
+        </is>
+      </c>
+      <c r="AG232" t="inlineStr">
+        <is>
+          <t>-34.48882963723285,172.68576684295184</t>
+        </is>
+      </c>
+      <c r="AH232" t="inlineStr">
+        <is>
+          <t>-34.48854140311783,172.6849393268061</t>
+        </is>
+      </c>
+      <c r="AI232" t="inlineStr">
+        <is>
+          <t>-34.48815467603941,172.68416075459993</t>
+        </is>
+      </c>
+      <c r="AJ232" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
